--- a/PRIZEPICKS_HITTER_AI_V4_ALL_PLAYERS_2026_07_16.xlsx
+++ b/PRIZEPICKS_HITTER_AI_V4_ALL_PLAYERS_2026_07_16.xlsx
@@ -1911,16 +1911,16 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>11.6</v>
+        <v>11.53</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>10.88</v>
+        <v>10.78</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>10.88</v>
+        <v>10.78</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>8.369999999999999</v>
@@ -1929,13 +1929,13 @@
         <v>7.57</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="P2" s="3" t="n">
         <v>7.57</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.836</v>
+        <v>0.846</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>6.2</v>
@@ -1962,88 +1962,88 @@
         </is>
       </c>
       <c r="X2" s="5" t="n">
-        <v>94.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>94.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="Z2" s="5" t="n">
-        <v>89.7</v>
+        <v>89.5</v>
       </c>
       <c r="AA2" s="5" t="n">
-        <v>89.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AB2" s="5" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="AC2" s="5" t="n">
-        <v>81.7</v>
+        <v>81.3</v>
       </c>
       <c r="AD2" s="5" t="n">
-        <v>77.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="AE2" s="5" t="n">
-        <v>68</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AF2" s="5" t="n">
-        <v>67.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG2" s="5" t="n">
-        <v>63.3</v>
+        <v>63</v>
       </c>
       <c r="AH2" s="5" t="n">
-        <v>62.8</v>
+        <v>62.5</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="AJ2" s="7" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="AK2" s="7" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="AL2" s="7" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="AM2" s="7" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="AN2" s="7" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="AO2" s="8" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="AP2" s="8" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="AQ2" s="8" t="n">
-        <v>36.2</v>
+        <v>35.9</v>
       </c>
       <c r="AR2" s="8" t="n">
-        <v>36.2</v>
+        <v>35.9</v>
       </c>
       <c r="AS2" s="8" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="AT2" s="8" t="n">
-        <v>30.2</v>
+        <v>34.5</v>
       </c>
       <c r="AU2" s="8" t="n">
-        <v>30.2</v>
+        <v>29.7</v>
       </c>
       <c r="AV2" s="8" t="n">
-        <v>29.1</v>
+        <v>28.5</v>
       </c>
       <c r="AW2" s="8" t="n">
-        <v>29.1</v>
+        <v>28.5</v>
       </c>
       <c r="AX2" s="8" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="AY2" s="3" t="n">
-        <v>268.14</v>
+        <v>266.56</v>
       </c>
       <c r="AZ2" s="4" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BA2" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.5 | 62.8% | Edge +3.4</t>
+          <t>MORE 7.5 | 62.5% | Edge +3.3</t>
         </is>
       </c>
       <c r="BB2" s="4" t="inlineStr">
@@ -2064,13 +2064,13 @@
         <v>7.5</v>
       </c>
       <c r="BD2" s="3" t="n">
-        <v>62.8</v>
+        <v>62.5</v>
       </c>
       <c r="BE2" s="3" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="BF2" s="3" t="n">
-        <v>25.6</v>
+        <v>25</v>
       </c>
       <c r="BG2" s="4" t="inlineStr">
         <is>
@@ -2165,23 +2165,23 @@
         <v>1.04</v>
       </c>
       <c r="CG2" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH2" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI2" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ2" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK2" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL2" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM2" s="3" t="n">
@@ -2303,19 +2303,19 @@
         <v>0.0161</v>
       </c>
       <c r="DW2" s="3" t="n">
-        <v>11.93</v>
+        <v>11.85</v>
       </c>
       <c r="DX2" s="3" t="n">
-        <v>12.17</v>
+        <v>12.09</v>
       </c>
       <c r="DY2" s="3" t="n">
-        <v>11.44</v>
+        <v>11.37</v>
       </c>
       <c r="DZ2" s="3" t="n">
-        <v>11.39</v>
+        <v>11.31</v>
       </c>
       <c r="EA2" s="3" t="n">
-        <v>11.04</v>
+        <v>10.96</v>
       </c>
       <c r="EB2" s="3" t="n">
         <v>28</v>
@@ -2377,13 +2377,13 @@
         <v>0.1541</v>
       </c>
       <c r="EU2" s="3" t="n">
-        <v>0.0511</v>
+        <v>0.0494</v>
       </c>
       <c r="EV2" s="3" t="n">
         <v>0.0046</v>
       </c>
       <c r="EW2" s="3" t="n">
-        <v>0.0712</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="EX2" s="3" t="n">
         <v>0.1282</v>
@@ -2424,13 +2424,13 @@
         <v>7.57</v>
       </c>
       <c r="FJ2" s="3" t="n">
-        <v>5.13</v>
+        <v>5.04</v>
       </c>
       <c r="FK2" s="3" t="n">
-        <v>15.16</v>
+        <v>15.2</v>
       </c>
       <c r="FL2" s="3" t="n">
-        <v>21.01</v>
+        <v>21.12</v>
       </c>
       <c r="FM2" s="3" t="n">
         <v>4.51</v>
@@ -2444,85 +2444,85 @@
         </is>
       </c>
       <c r="FP2" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="FQ2" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="FR2" s="3" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="FS2" s="3" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="FT2" s="3" t="n">
-        <v>76.7</v>
+        <v>76.3</v>
       </c>
       <c r="FU2" s="3" t="n">
-        <v>76.7</v>
+        <v>76.3</v>
       </c>
       <c r="FV2" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="FW2" s="3" t="n">
-        <v>64</v>
+        <v>63.4</v>
       </c>
       <c r="FX2" s="3" t="n">
-        <v>64</v>
+        <v>63.4</v>
       </c>
       <c r="FY2" s="3" t="n">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="FZ2" s="3" t="n">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="GA2" s="3" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="GB2" s="3" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="GC2" s="3" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="GD2" s="3" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="GE2" s="3" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="GF2" s="3" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="GG2" s="3" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="GH2" s="3" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="GI2" s="3" t="n">
-        <v>36.2</v>
+        <v>35.9</v>
       </c>
       <c r="GJ2" s="3" t="n">
-        <v>36.2</v>
+        <v>35.9</v>
       </c>
       <c r="GK2" s="3" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="GL2" s="3" t="n">
-        <v>30.2</v>
+        <v>34.5</v>
       </c>
       <c r="GM2" s="3" t="n">
-        <v>30.2</v>
+        <v>29.7</v>
       </c>
       <c r="GN2" s="3" t="n">
-        <v>29.1</v>
+        <v>28.5</v>
       </c>
       <c r="GO2" s="3" t="n">
-        <v>29.1</v>
+        <v>28.5</v>
       </c>
       <c r="GP2" s="3" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="GQ2" s="3" t="n">
         <v>4</v>
@@ -2531,10 +2531,10 @@
         <v>4</v>
       </c>
       <c r="GS2" s="3" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="GT2" s="3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="GU2" s="3" t="n">
         <v>6</v>
@@ -2651,16 +2651,16 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>10.03</v>
+        <v>9.91</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>9.08</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>9.08</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>7.91</v>
@@ -2669,13 +2669,13 @@
         <v>7.25</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>7.88</v>
+        <v>7.85</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>7.25</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.92</v>
+        <v>0.924</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>7.4</v>
@@ -2702,88 +2702,88 @@
         </is>
       </c>
       <c r="X3" s="5" t="n">
-        <v>91.5</v>
+        <v>90.7</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>88.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>78.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="AA3" s="5" t="n">
-        <v>78.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="AB3" s="5" t="n">
-        <v>73.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AC3" s="5" t="n">
-        <v>72.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AD3" s="5" t="n">
-        <v>61.7</v>
+        <v>60.1</v>
       </c>
       <c r="AE3" s="5" t="n">
-        <v>61.2</v>
+        <v>59.6</v>
       </c>
       <c r="AF3" s="6" t="n">
-        <v>57.7</v>
+        <v>55.7</v>
       </c>
       <c r="AG3" s="7" t="n">
-        <v>57.2</v>
+        <v>55.2</v>
       </c>
       <c r="AH3" s="7" t="n">
-        <v>49.6</v>
+        <v>47.6</v>
       </c>
       <c r="AI3" s="7" t="n">
-        <v>48.1</v>
+        <v>46.1</v>
       </c>
       <c r="AJ3" s="7" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="AK3" s="7" t="n">
-        <v>42.3</v>
+        <v>40.5</v>
+      </c>
+      <c r="AK3" s="8" t="n">
+        <v>37.1</v>
       </c>
       <c r="AL3" s="8" t="n">
-        <v>38.5</v>
+        <v>37.1</v>
       </c>
       <c r="AM3" s="8" t="n">
-        <v>33.8</v>
+        <v>32.2</v>
       </c>
       <c r="AN3" s="8" t="n">
-        <v>33.8</v>
+        <v>32.2</v>
       </c>
       <c r="AO3" s="8" t="n">
-        <v>31.6</v>
+        <v>30.1</v>
       </c>
       <c r="AP3" s="8" t="n">
-        <v>31.6</v>
+        <v>30.1</v>
       </c>
       <c r="AQ3" s="8" t="n">
-        <v>28.3</v>
+        <v>26.9</v>
       </c>
       <c r="AR3" s="8" t="n">
-        <v>28.3</v>
+        <v>26.9</v>
       </c>
       <c r="AS3" s="8" t="n">
-        <v>26.5</v>
+        <v>25.2</v>
       </c>
       <c r="AT3" s="8" t="n">
-        <v>26.5</v>
+        <v>25.2</v>
       </c>
       <c r="AU3" s="8" t="n">
-        <v>21.9</v>
+        <v>20.8</v>
       </c>
       <c r="AV3" s="8" t="n">
-        <v>21.9</v>
+        <v>20.8</v>
       </c>
       <c r="AW3" s="8" t="n">
-        <v>20.4</v>
+        <v>19.4</v>
       </c>
       <c r="AX3" s="8" t="n">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="AY3" s="3" t="n">
-        <v>232.75</v>
+        <v>227.94</v>
       </c>
       <c r="AZ3" s="4" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="BA3" s="9" t="inlineStr">
         <is>
-          <t>MORE 6.0 | 61.2% | Edge +3.1</t>
+          <t>MORE 6.0 | 59.6% | Edge +2.8</t>
         </is>
       </c>
       <c r="BB3" s="4" t="inlineStr">
@@ -2804,13 +2804,13 @@
         <v>6</v>
       </c>
       <c r="BD3" s="3" t="n">
-        <v>61.2</v>
+        <v>59.6</v>
       </c>
       <c r="BE3" s="3" t="n">
-        <v>3.08</v>
+        <v>2.79</v>
       </c>
       <c r="BF3" s="3" t="n">
-        <v>22.4</v>
+        <v>19.2</v>
       </c>
       <c r="BG3" s="4" t="inlineStr">
         <is>
@@ -2905,23 +2905,23 @@
         <v>1.04</v>
       </c>
       <c r="CG3" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH3" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI3" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ3" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK3" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL3" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM3" s="3" t="n">
@@ -3043,19 +3043,19 @@
         <v>0.0179</v>
       </c>
       <c r="DW3" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DX3" s="3" t="n">
-        <v>10.6</v>
+        <v>10.46</v>
       </c>
       <c r="DY3" s="3" t="n">
-        <v>10.6</v>
+        <v>10.47</v>
       </c>
       <c r="DZ3" s="3" t="n">
-        <v>10.49</v>
+        <v>10.36</v>
       </c>
       <c r="EA3" s="3" t="n">
-        <v>8.85</v>
+        <v>8.74</v>
       </c>
       <c r="EB3" s="3" t="n">
         <v>28</v>
@@ -3117,13 +3117,13 @@
         <v>0.1631</v>
       </c>
       <c r="EU3" s="3" t="n">
-        <v>0.0517</v>
+        <v>0.05</v>
       </c>
       <c r="EV3" s="3" t="n">
         <v>0.0038</v>
       </c>
       <c r="EW3" s="3" t="n">
-        <v>0.0471</v>
+        <v>0.0456</v>
       </c>
       <c r="EX3" s="3" t="n">
         <v>0.0742</v>
@@ -3164,13 +3164,13 @@
         <v>7.25</v>
       </c>
       <c r="FJ3" s="3" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="FK3" s="3" t="n">
-        <v>13.61</v>
+        <v>13.6</v>
       </c>
       <c r="FL3" s="3" t="n">
-        <v>19.13</v>
+        <v>19.15</v>
       </c>
       <c r="FM3" s="3" t="n">
         <v>4.62</v>
@@ -3184,91 +3184,91 @@
         </is>
       </c>
       <c r="FP3" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="FQ3" s="3" t="n">
-        <v>80.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="FR3" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="FS3" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="FT3" s="3" t="n">
-        <v>67.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="FU3" s="3" t="n">
-        <v>67.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="FV3" s="3" t="n">
-        <v>57.2</v>
+        <v>55.6</v>
       </c>
       <c r="FW3" s="3" t="n">
-        <v>57.2</v>
+        <v>55.6</v>
       </c>
       <c r="FX3" s="3" t="n">
-        <v>54.2</v>
+        <v>52.2</v>
       </c>
       <c r="FY3" s="3" t="n">
-        <v>54.2</v>
+        <v>52.2</v>
       </c>
       <c r="FZ3" s="3" t="n">
-        <v>47.1</v>
+        <v>45.1</v>
       </c>
       <c r="GA3" s="3" t="n">
-        <v>47.1</v>
+        <v>45.1</v>
       </c>
       <c r="GB3" s="3" t="n">
-        <v>42.3</v>
+        <v>40.5</v>
       </c>
       <c r="GC3" s="3" t="n">
-        <v>42.3</v>
+        <v>37.1</v>
       </c>
       <c r="GD3" s="3" t="n">
-        <v>38.5</v>
+        <v>37.1</v>
       </c>
       <c r="GE3" s="3" t="n">
-        <v>33.8</v>
+        <v>32.2</v>
       </c>
       <c r="GF3" s="3" t="n">
-        <v>33.8</v>
+        <v>32.2</v>
       </c>
       <c r="GG3" s="3" t="n">
-        <v>31.6</v>
+        <v>30.1</v>
       </c>
       <c r="GH3" s="3" t="n">
-        <v>31.6</v>
+        <v>30.1</v>
       </c>
       <c r="GI3" s="3" t="n">
-        <v>28.3</v>
+        <v>26.9</v>
       </c>
       <c r="GJ3" s="3" t="n">
-        <v>28.3</v>
+        <v>26.9</v>
       </c>
       <c r="GK3" s="3" t="n">
-        <v>26.5</v>
+        <v>25.2</v>
       </c>
       <c r="GL3" s="3" t="n">
-        <v>26.5</v>
+        <v>25.2</v>
       </c>
       <c r="GM3" s="3" t="n">
-        <v>21.9</v>
+        <v>20.8</v>
       </c>
       <c r="GN3" s="3" t="n">
-        <v>21.9</v>
+        <v>20.8</v>
       </c>
       <c r="GO3" s="3" t="n">
-        <v>20.4</v>
+        <v>19.4</v>
       </c>
       <c r="GP3" s="3" t="n">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="GQ3" s="3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="GR3" s="3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="GS3" s="3" t="n">
         <v>7.5</v>
@@ -3391,16 +3391,16 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>9.779999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>8.460000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8.460000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>6.21</v>
+        <v>5.34</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>8.119999999999999</v>
@@ -3409,13 +3409,13 @@
         <v>7.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>8.09</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.914</v>
+        <v>0.902</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>6.4</v>
@@ -3442,43 +3442,43 @@
         </is>
       </c>
       <c r="X4" s="5" t="n">
-        <v>91.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>82.2</v>
+        <v>81.2</v>
       </c>
       <c r="Z4" s="5" t="n">
-        <v>74</v>
+        <v>80.7</v>
       </c>
       <c r="AA4" s="5" t="n">
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="AB4" s="5" t="n">
-        <v>65.8</v>
+        <v>65</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>64.8</v>
+        <v>64</v>
       </c>
       <c r="AD4" s="6" t="n">
-        <v>55.1</v>
+        <v>54.3</v>
       </c>
       <c r="AE4" s="7" t="n">
-        <v>54.6</v>
+        <v>53.8</v>
       </c>
       <c r="AF4" s="7" t="n">
-        <v>49.7</v>
+        <v>49.3</v>
       </c>
       <c r="AG4" s="7" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="AH4" s="7" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="AI4" s="7" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="AJ4" s="8" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="AK4" s="8" t="n">
         <v>33</v>
@@ -3487,16 +3487,16 @@
         <v>33</v>
       </c>
       <c r="AM4" s="8" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="AN4" s="8" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="AO4" s="8" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="AP4" s="8" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="AQ4" s="8" t="n">
         <v>27.1</v>
@@ -3505,25 +3505,25 @@
         <v>27.1</v>
       </c>
       <c r="AS4" s="8" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="AT4" s="8" t="n">
-        <v>26</v>
+        <v>21.8</v>
       </c>
       <c r="AU4" s="8" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="AV4" s="8" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="AW4" s="8" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="AX4" s="8" t="n">
-        <v>16.8</v>
+        <v>17.5</v>
       </c>
       <c r="AY4" s="3" t="n">
-        <v>214.33</v>
+        <v>214</v>
       </c>
       <c r="AZ4" s="4" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="BA4" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 64.8% | Edge +3.5</t>
+          <t>MORE 5.0 | 64.0% | Edge +3.4</t>
         </is>
       </c>
       <c r="BB4" s="4" t="inlineStr">
@@ -3544,13 +3544,13 @@
         <v>5</v>
       </c>
       <c r="BD4" s="3" t="n">
-        <v>64.8</v>
+        <v>64</v>
       </c>
       <c r="BE4" s="3" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="BF4" s="3" t="n">
-        <v>29.6</v>
+        <v>28</v>
       </c>
       <c r="BG4" s="4" t="inlineStr">
         <is>
@@ -3645,23 +3645,23 @@
         <v>1.04</v>
       </c>
       <c r="CG4" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH4" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI4" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ4" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK4" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL4" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM4" s="3" t="n">
@@ -3783,19 +3783,19 @@
         <v>0.0159</v>
       </c>
       <c r="DW4" s="3" t="n">
-        <v>10.68</v>
+        <v>10.54</v>
       </c>
       <c r="DX4" s="3" t="n">
-        <v>10.24</v>
+        <v>10.13</v>
       </c>
       <c r="DY4" s="3" t="n">
-        <v>9.02</v>
+        <v>8.92</v>
       </c>
       <c r="DZ4" s="3" t="n">
-        <v>9.08</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="EA4" s="3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="EB4" s="3" t="n">
         <v>28</v>
@@ -3857,13 +3857,13 @@
         <v>0.1211</v>
       </c>
       <c r="EU4" s="3" t="n">
-        <v>0.0298</v>
+        <v>0.0288</v>
       </c>
       <c r="EV4" s="3" t="n">
         <v>0.0027</v>
       </c>
       <c r="EW4" s="3" t="n">
-        <v>0.0595</v>
+        <v>0.0576</v>
       </c>
       <c r="EX4" s="3" t="n">
         <v>0.1398</v>
@@ -3904,16 +3904,16 @@
         <v>7.4</v>
       </c>
       <c r="FJ4" s="3" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="FK4" s="3" t="n">
-        <v>13.53</v>
+        <v>13.46</v>
       </c>
       <c r="FL4" s="3" t="n">
-        <v>19.01</v>
+        <v>18.87</v>
       </c>
       <c r="FM4" s="3" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="FN4" s="3" t="n">
         <v>0</v>
@@ -3924,43 +3924,43 @@
         </is>
       </c>
       <c r="FP4" s="3" t="n">
-        <v>85.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="FQ4" s="3" t="n">
-        <v>74.2</v>
+        <v>73.2</v>
       </c>
       <c r="FR4" s="3" t="n">
-        <v>66.5</v>
+        <v>73.2</v>
       </c>
       <c r="FS4" s="3" t="n">
-        <v>66.5</v>
+        <v>65.5</v>
       </c>
       <c r="FT4" s="3" t="n">
-        <v>59.8</v>
+        <v>59</v>
       </c>
       <c r="FU4" s="3" t="n">
-        <v>59.8</v>
+        <v>59</v>
       </c>
       <c r="FV4" s="3" t="n">
-        <v>50.6</v>
+        <v>49.8</v>
       </c>
       <c r="FW4" s="3" t="n">
-        <v>50.6</v>
+        <v>49.8</v>
       </c>
       <c r="FX4" s="3" t="n">
-        <v>46.2</v>
+        <v>45.8</v>
       </c>
       <c r="FY4" s="3" t="n">
-        <v>46.2</v>
+        <v>45.8</v>
       </c>
       <c r="FZ4" s="3" t="n">
-        <v>40.1</v>
+        <v>39.8</v>
       </c>
       <c r="GA4" s="3" t="n">
-        <v>40.1</v>
+        <v>39.8</v>
       </c>
       <c r="GB4" s="3" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="GC4" s="3" t="n">
         <v>33</v>
@@ -3969,16 +3969,16 @@
         <v>33</v>
       </c>
       <c r="GE4" s="3" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="GF4" s="3" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="GG4" s="3" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="GH4" s="3" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="GI4" s="3" t="n">
         <v>27.1</v>
@@ -3987,25 +3987,25 @@
         <v>27.1</v>
       </c>
       <c r="GK4" s="3" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="GL4" s="3" t="n">
-        <v>26</v>
+        <v>21.8</v>
       </c>
       <c r="GM4" s="3" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="GN4" s="3" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="GO4" s="3" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="GP4" s="3" t="n">
-        <v>16.8</v>
+        <v>17.5</v>
       </c>
       <c r="GQ4" s="3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="GR4" s="3" t="n">
         <v>8</v>
@@ -4131,16 +4131,16 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>7.99</v>
+        <v>7.92</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>7.99</v>
+        <v>7.92</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>6.26</v>
+        <v>6.23</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>6.74</v>
@@ -4149,13 +4149,13 @@
         <v>6.47</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>7.43</v>
+        <v>7.35</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>6.47</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.871</v>
+        <v>0.88</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>8.800000000000001</v>
@@ -4182,19 +4182,19 @@
         </is>
       </c>
       <c r="X5" s="5" t="n">
-        <v>89.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>83.7</v>
+        <v>83.3</v>
       </c>
       <c r="AA5" s="5" t="n">
-        <v>71.7</v>
+        <v>72</v>
       </c>
       <c r="AB5" s="5" t="n">
-        <v>70.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AC5" s="5" t="n">
         <v>66.90000000000001</v>
@@ -4215,55 +4215,55 @@
         <v>43.6</v>
       </c>
       <c r="AI5" s="8" t="n">
-        <v>37.4</v>
+        <v>36.6</v>
       </c>
       <c r="AJ5" s="8" t="n">
-        <v>36.4</v>
+        <v>35.6</v>
       </c>
       <c r="AK5" s="8" t="n">
-        <v>32.8</v>
+        <v>32.4</v>
       </c>
       <c r="AL5" s="8" t="n">
-        <v>32.8</v>
+        <v>32.4</v>
       </c>
       <c r="AM5" s="8" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="AN5" s="8" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="AO5" s="8" t="n">
-        <v>26.3</v>
+        <v>25.7</v>
       </c>
       <c r="AP5" s="8" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="AQ5" s="8" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="AR5" s="8" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="AS5" s="8" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="AT5" s="8" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="AU5" s="8" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="AV5" s="8" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="AW5" s="8" t="n">
-        <v>13.9</v>
+        <v>16.2</v>
       </c>
       <c r="AX5" s="8" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="AY5" s="3" t="n">
-        <v>213.47</v>
+        <v>212.32</v>
       </c>
       <c r="AZ5" s="4" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="BA5" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 66.9% | Edge +3.0</t>
+          <t>MORE 5.0 | 66.9% | Edge +2.9</t>
         </is>
       </c>
       <c r="BB5" s="4" t="inlineStr">
@@ -4287,7 +4287,7 @@
         <v>66.90000000000001</v>
       </c>
       <c r="BE5" s="3" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="BF5" s="3" t="n">
         <v>33.8</v>
@@ -4385,23 +4385,23 @@
         <v>1.04</v>
       </c>
       <c r="CG5" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH5" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI5" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ5" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK5" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL5" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM5" s="3" t="n">
@@ -4523,19 +4523,19 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="DW5" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="DX5" s="3" t="n">
-        <v>9.279999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="DY5" s="3" t="n">
-        <v>9.720000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DZ5" s="3" t="n">
-        <v>10.25</v>
+        <v>10.14</v>
       </c>
       <c r="EA5" s="3" t="n">
-        <v>8.050000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="EB5" s="3" t="n">
         <v>28</v>
@@ -4597,13 +4597,13 @@
         <v>0.18</v>
       </c>
       <c r="EU5" s="3" t="n">
-        <v>0.0473</v>
+        <v>0.0458</v>
       </c>
       <c r="EV5" s="3" t="n">
         <v>0.005</v>
       </c>
       <c r="EW5" s="3" t="n">
-        <v>0.0432</v>
+        <v>0.0418</v>
       </c>
       <c r="EX5" s="3" t="n">
         <v>0.0764</v>
@@ -4644,16 +4644,16 @@
         <v>6.47</v>
       </c>
       <c r="FJ5" s="3" t="n">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="FK5" s="3" t="n">
-        <v>11.48</v>
+        <v>11.51</v>
       </c>
       <c r="FL5" s="3" t="n">
-        <v>17.58</v>
+        <v>17.67</v>
       </c>
       <c r="FM5" s="3" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="FN5" s="3" t="n">
         <v>0</v>
@@ -4664,19 +4664,19 @@
         </is>
       </c>
       <c r="FP5" s="3" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="FQ5" s="3" t="n">
-        <v>76.2</v>
+        <v>75.8</v>
       </c>
       <c r="FR5" s="3" t="n">
-        <v>76.2</v>
+        <v>75.8</v>
       </c>
       <c r="FS5" s="3" t="n">
-        <v>64.7</v>
+        <v>65</v>
       </c>
       <c r="FT5" s="3" t="n">
-        <v>64.7</v>
+        <v>61.9</v>
       </c>
       <c r="FU5" s="3" t="n">
         <v>61.9</v>
@@ -4697,55 +4697,55 @@
         <v>41.1</v>
       </c>
       <c r="GA5" s="3" t="n">
-        <v>36.4</v>
+        <v>35.6</v>
       </c>
       <c r="GB5" s="3" t="n">
-        <v>36.4</v>
+        <v>35.6</v>
       </c>
       <c r="GC5" s="3" t="n">
-        <v>32.8</v>
+        <v>32.4</v>
       </c>
       <c r="GD5" s="3" t="n">
-        <v>32.8</v>
+        <v>32.4</v>
       </c>
       <c r="GE5" s="3" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="GF5" s="3" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="GG5" s="3" t="n">
-        <v>26.3</v>
+        <v>25.7</v>
       </c>
       <c r="GH5" s="3" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="GI5" s="3" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="GJ5" s="3" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="GK5" s="3" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="GL5" s="3" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="GM5" s="3" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="GN5" s="3" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="GO5" s="3" t="n">
-        <v>13.9</v>
+        <v>16.2</v>
       </c>
       <c r="GP5" s="3" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="GQ5" s="3" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="GR5" s="3" t="n">
         <v>8</v>
@@ -4871,16 +4871,16 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>6.42</v>
+        <v>5.55</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>6.84</v>
@@ -4889,13 +4889,13 @@
         <v>6.54</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>7.99</v>
+        <v>7.92</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>6.54</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>6.2</v>
@@ -4922,88 +4922,88 @@
         </is>
       </c>
       <c r="X6" s="5" t="n">
-        <v>88.8</v>
+        <v>88.5</v>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>88.8</v>
+        <v>88.5</v>
       </c>
       <c r="Z6" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AA6" s="5" t="n">
-        <v>71</v>
+        <v>70.2</v>
       </c>
       <c r="AB6" s="5" t="n">
-        <v>70</v>
+        <v>69.2</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>65.8</v>
+        <v>64.8</v>
       </c>
       <c r="AD6" s="5" t="n">
-        <v>65.3</v>
+        <v>64.3</v>
       </c>
       <c r="AE6" s="6" t="n">
-        <v>54.8</v>
+        <v>54</v>
       </c>
       <c r="AF6" s="7" t="n">
-        <v>51.4</v>
+        <v>50.3</v>
       </c>
       <c r="AG6" s="7" t="n">
-        <v>50.9</v>
+        <v>49.8</v>
       </c>
       <c r="AH6" s="7" t="n">
-        <v>44.1</v>
+        <v>43.2</v>
       </c>
       <c r="AI6" s="7" t="n">
-        <v>42.6</v>
+        <v>41.7</v>
       </c>
       <c r="AJ6" s="8" t="n">
-        <v>37.4</v>
+        <v>36.7</v>
       </c>
       <c r="AK6" s="8" t="n">
-        <v>34.1</v>
+        <v>33.3</v>
       </c>
       <c r="AL6" s="8" t="n">
-        <v>34.1</v>
+        <v>33.3</v>
       </c>
       <c r="AM6" s="8" t="n">
-        <v>30.2</v>
+        <v>29.3</v>
       </c>
       <c r="AN6" s="8" t="n">
-        <v>30.2</v>
+        <v>29.3</v>
       </c>
       <c r="AO6" s="8" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
       <c r="AP6" s="8" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="AQ6" s="8" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="AR6" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="AS6" s="8" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="AT6" s="8" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="AU6" s="8" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="AV6" s="8" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="AW6" s="8" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="AX6" s="8" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="AY6" s="3" t="n">
-        <v>210.62</v>
+        <v>208.27</v>
       </c>
       <c r="AZ6" s="4" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="BA6" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.5 | 65.3% | Edge +2.8</t>
+          <t>MORE 5.5 | 64.3% | Edge +2.7</t>
         </is>
       </c>
       <c r="BB6" s="4" t="inlineStr">
@@ -5024,13 +5024,13 @@
         <v>5.5</v>
       </c>
       <c r="BD6" s="3" t="n">
-        <v>65.3</v>
+        <v>64.3</v>
       </c>
       <c r="BE6" s="3" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="BF6" s="3" t="n">
-        <v>30.6</v>
+        <v>28.6</v>
       </c>
       <c r="BG6" s="4" t="inlineStr">
         <is>
@@ -5125,23 +5125,23 @@
         <v>1.04</v>
       </c>
       <c r="CG6" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH6" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI6" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ6" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK6" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL6" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM6" s="3" t="n">
@@ -5263,19 +5263,19 @@
         <v>0</v>
       </c>
       <c r="DW6" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="DX6" s="3" t="n">
-        <v>9.58</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DY6" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="DZ6" s="3" t="n">
-        <v>9.279999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="EA6" s="3" t="n">
-        <v>8.630000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="EB6" s="3" t="n">
         <v>28</v>
@@ -5337,13 +5337,13 @@
         <v>0.1488</v>
       </c>
       <c r="EU6" s="3" t="n">
-        <v>0.0465</v>
+        <v>0.045</v>
       </c>
       <c r="EV6" s="3" t="n">
         <v>0.0077</v>
       </c>
       <c r="EW6" s="3" t="n">
-        <v>0.0504</v>
+        <v>0.0487</v>
       </c>
       <c r="EX6" s="3" t="n">
         <v>0.07140000000000001</v>
@@ -5384,13 +5384,13 @@
         <v>6.54</v>
       </c>
       <c r="FJ6" s="3" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="FK6" s="3" t="n">
         <v>12.15</v>
       </c>
       <c r="FL6" s="3" t="n">
-        <v>17.06</v>
+        <v>17.11</v>
       </c>
       <c r="FM6" s="3" t="n">
         <v>4.33</v>
@@ -5404,91 +5404,91 @@
         </is>
       </c>
       <c r="FP6" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="FQ6" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="FR6" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="FS6" s="3" t="n">
-        <v>64</v>
+        <v>63.2</v>
       </c>
       <c r="FT6" s="3" t="n">
-        <v>64</v>
+        <v>63.2</v>
       </c>
       <c r="FU6" s="3" t="n">
-        <v>60.8</v>
+        <v>59.8</v>
       </c>
       <c r="FV6" s="3" t="n">
-        <v>60.8</v>
+        <v>59.8</v>
       </c>
       <c r="FW6" s="3" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="FX6" s="3" t="n">
-        <v>47.9</v>
+        <v>46.8</v>
       </c>
       <c r="FY6" s="3" t="n">
-        <v>47.9</v>
+        <v>46.8</v>
       </c>
       <c r="FZ6" s="3" t="n">
-        <v>41.6</v>
+        <v>40.7</v>
       </c>
       <c r="GA6" s="3" t="n">
-        <v>41.6</v>
+        <v>40.7</v>
       </c>
       <c r="GB6" s="3" t="n">
-        <v>37.4</v>
+        <v>36.7</v>
       </c>
       <c r="GC6" s="3" t="n">
-        <v>34.1</v>
+        <v>33.3</v>
       </c>
       <c r="GD6" s="3" t="n">
-        <v>34.1</v>
+        <v>33.3</v>
       </c>
       <c r="GE6" s="3" t="n">
-        <v>30.2</v>
+        <v>29.3</v>
       </c>
       <c r="GF6" s="3" t="n">
-        <v>30.2</v>
+        <v>29.3</v>
       </c>
       <c r="GG6" s="3" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
       <c r="GH6" s="3" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="GI6" s="3" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="GJ6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="GK6" s="3" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="GL6" s="3" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="GM6" s="3" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="GN6" s="3" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="GO6" s="3" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="GP6" s="3" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="GQ6" s="3" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="GR6" s="3" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="GS6" s="3" t="n">
         <v>7.5</v>
@@ -5611,16 +5611,16 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8.98</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.6</v>
+        <v>7.52</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>7.6</v>
+        <v>7.52</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>6.7</v>
@@ -5629,13 +5629,13 @@
         <v>6.44</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>6.44</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.908</v>
+        <v>0.91</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>2.4</v>
@@ -5662,88 +5662,88 @@
         </is>
       </c>
       <c r="X7" s="5" t="n">
-        <v>88.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>71.5</v>
+        <v>70.3</v>
       </c>
       <c r="AA7" s="5" t="n">
-        <v>71</v>
+        <v>69.8</v>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>67.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="AD7" s="6" t="n">
-        <v>54.2</v>
+        <v>53.7</v>
       </c>
       <c r="AE7" s="7" t="n">
-        <v>53.7</v>
+        <v>53.2</v>
       </c>
       <c r="AF7" s="7" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="AG7" s="7" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="AH7" s="7" t="n">
-        <v>41.8</v>
+        <v>41.3</v>
       </c>
       <c r="AI7" s="8" t="n">
-        <v>35.1</v>
+        <v>34.4</v>
       </c>
       <c r="AJ7" s="8" t="n">
-        <v>34.1</v>
+        <v>33.4</v>
       </c>
       <c r="AK7" s="8" t="n">
-        <v>30.6</v>
+        <v>29.8</v>
       </c>
       <c r="AL7" s="8" t="n">
-        <v>30.6</v>
+        <v>29.8</v>
       </c>
       <c r="AM7" s="8" t="n">
-        <v>26.2</v>
+        <v>25.5</v>
       </c>
       <c r="AN7" s="8" t="n">
-        <v>26.2</v>
+        <v>25.5</v>
       </c>
       <c r="AO7" s="8" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
       <c r="AP7" s="8" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
       <c r="AQ7" s="8" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="AR7" s="8" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="AS7" s="8" t="n">
-        <v>19.8</v>
+        <v>18.9</v>
       </c>
       <c r="AT7" s="8" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="AU7" s="8" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="AV7" s="8" t="n">
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="AW7" s="8" t="n">
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="AX7" s="8" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="AY7" s="3" t="n">
-        <v>196.24</v>
+        <v>194.86</v>
       </c>
       <c r="AZ7" s="4" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="BA7" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 66.1% | Edge +2.6</t>
+          <t>MORE 5.0 | 65.0% | Edge +2.5</t>
         </is>
       </c>
       <c r="BB7" s="4" t="inlineStr">
@@ -5764,13 +5764,13 @@
         <v>5</v>
       </c>
       <c r="BD7" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="BE7" s="3" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="BF7" s="3" t="n">
-        <v>32.2</v>
+        <v>30</v>
       </c>
       <c r="BG7" s="4" t="inlineStr">
         <is>
@@ -5865,23 +5865,23 @@
         <v>1.04</v>
       </c>
       <c r="CG7" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH7" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI7" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ7" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK7" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL7" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM7" s="3" t="n">
@@ -6003,19 +6003,19 @@
         <v>0</v>
       </c>
       <c r="DW7" s="3" t="n">
-        <v>9.02</v>
+        <v>8.93</v>
       </c>
       <c r="DX7" s="3" t="n">
-        <v>10.29</v>
+        <v>10.18</v>
       </c>
       <c r="DY7" s="3" t="n">
-        <v>8.66</v>
+        <v>8.59</v>
       </c>
       <c r="DZ7" s="3" t="n">
-        <v>9.26</v>
+        <v>9.17</v>
       </c>
       <c r="EA7" s="3" t="n">
-        <v>7.98</v>
+        <v>7.89</v>
       </c>
       <c r="EB7" s="3" t="n">
         <v>28</v>
@@ -6077,13 +6077,13 @@
         <v>0.1785</v>
       </c>
       <c r="EU7" s="3" t="n">
-        <v>0.0452</v>
+        <v>0.0437</v>
       </c>
       <c r="EV7" s="3" t="n">
         <v>0.0037</v>
       </c>
       <c r="EW7" s="3" t="n">
-        <v>0.0338</v>
+        <v>0.0327</v>
       </c>
       <c r="EX7" s="3" t="n">
         <v>0.0619</v>
@@ -6124,13 +6124,13 @@
         <v>6.44</v>
       </c>
       <c r="FJ7" s="3" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="FK7" s="3" t="n">
         <v>10.69</v>
       </c>
       <c r="FL7" s="3" t="n">
-        <v>17.04</v>
+        <v>17.05</v>
       </c>
       <c r="FM7" s="3" t="n">
         <v>4.42</v>
@@ -6144,88 +6144,88 @@
         </is>
       </c>
       <c r="FP7" s="3" t="n">
-        <v>81.5</v>
+        <v>75.8</v>
       </c>
       <c r="FQ7" s="3" t="n">
-        <v>76</v>
+        <v>75.8</v>
       </c>
       <c r="FR7" s="3" t="n">
-        <v>64</v>
+        <v>62.8</v>
       </c>
       <c r="FS7" s="3" t="n">
-        <v>64</v>
+        <v>62.8</v>
       </c>
       <c r="FT7" s="3" t="n">
-        <v>61.1</v>
+        <v>60</v>
       </c>
       <c r="FU7" s="3" t="n">
-        <v>61.1</v>
+        <v>60</v>
       </c>
       <c r="FV7" s="3" t="n">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
       <c r="FW7" s="3" t="n">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
       <c r="FX7" s="3" t="n">
-        <v>45.8</v>
+        <v>45.4</v>
       </c>
       <c r="FY7" s="3" t="n">
-        <v>45.8</v>
+        <v>45.4</v>
       </c>
       <c r="FZ7" s="3" t="n">
-        <v>39.3</v>
+        <v>38.8</v>
       </c>
       <c r="GA7" s="3" t="n">
-        <v>34.1</v>
+        <v>33.4</v>
       </c>
       <c r="GB7" s="3" t="n">
-        <v>34.1</v>
+        <v>33.4</v>
       </c>
       <c r="GC7" s="3" t="n">
-        <v>30.6</v>
+        <v>29.8</v>
       </c>
       <c r="GD7" s="3" t="n">
-        <v>30.6</v>
+        <v>29.8</v>
       </c>
       <c r="GE7" s="3" t="n">
-        <v>26.2</v>
+        <v>25.5</v>
       </c>
       <c r="GF7" s="3" t="n">
-        <v>26.2</v>
+        <v>25.5</v>
       </c>
       <c r="GG7" s="3" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
       <c r="GH7" s="3" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
       <c r="GI7" s="3" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="GJ7" s="3" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="GK7" s="3" t="n">
-        <v>19.8</v>
+        <v>18.9</v>
       </c>
       <c r="GL7" s="3" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="GM7" s="3" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="GN7" s="3" t="n">
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="GO7" s="3" t="n">
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="GP7" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="GQ7" s="3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="GR7" s="3" t="n">
         <v>8</v>
@@ -6351,16 +6351,16 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.98</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>7.45</v>
+        <v>7.31</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>7.45</v>
+        <v>7.31</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4.95</v>
+        <v>4.88</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>8.16</v>
@@ -6369,13 +6369,13 @@
         <v>7.42</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>7.33</v>
+        <v>7.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>7.4</v>
+        <v>7.37</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.012</v>
+        <v>1.031</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>4.6</v>
@@ -6402,88 +6402,88 @@
         </is>
       </c>
       <c r="X8" s="5" t="n">
-        <v>78.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>71.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="Z8" s="5" t="n">
-        <v>70.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AA8" s="5" t="n">
-        <v>62.7</v>
+        <v>61.9</v>
       </c>
       <c r="AB8" s="5" t="n">
-        <v>61.7</v>
+        <v>60.9</v>
       </c>
       <c r="AC8" s="6" t="n">
-        <v>51.7</v>
+        <v>50.7</v>
       </c>
       <c r="AD8" s="7" t="n">
-        <v>51.2</v>
+        <v>50.2</v>
       </c>
       <c r="AE8" s="7" t="n">
-        <v>47</v>
+        <v>45.7</v>
       </c>
       <c r="AF8" s="7" t="n">
-        <v>46.5</v>
+        <v>45.2</v>
       </c>
       <c r="AG8" s="8" t="n">
-        <v>38.9</v>
+        <v>37.7</v>
       </c>
       <c r="AH8" s="8" t="n">
-        <v>38.4</v>
+        <v>37.2</v>
       </c>
       <c r="AI8" s="8" t="n">
-        <v>33.6</v>
+        <v>32.8</v>
       </c>
       <c r="AJ8" s="8" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="AK8" s="8" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="AL8" s="8" t="n">
-        <v>28.1</v>
+        <v>27.6</v>
       </c>
       <c r="AM8" s="8" t="n">
-        <v>28.1</v>
+        <v>27.6</v>
       </c>
       <c r="AN8" s="8" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="AO8" s="8" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="AP8" s="8" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AQ8" s="8" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AR8" s="8" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="AS8" s="8" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="AT8" s="8" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AU8" s="8" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AV8" s="8" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="AW8" s="8" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="AX8" s="8" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="AY8" s="3" t="n">
-        <v>190.91</v>
+        <v>188.48</v>
       </c>
       <c r="AZ8" s="4" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="BA8" s="9" t="inlineStr">
         <is>
-          <t>MORE 4.5 | 61.7% | Edge +3.0</t>
+          <t>MORE 4.5 | 60.9% | Edge +2.8</t>
         </is>
       </c>
       <c r="BB8" s="4" t="inlineStr">
@@ -6504,13 +6504,13 @@
         <v>4.5</v>
       </c>
       <c r="BD8" s="3" t="n">
-        <v>61.7</v>
+        <v>60.9</v>
       </c>
       <c r="BE8" s="3" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="BF8" s="3" t="n">
-        <v>23.4</v>
+        <v>21.8</v>
       </c>
       <c r="BG8" s="4" t="inlineStr">
         <is>
@@ -6605,23 +6605,23 @@
         <v>1.04</v>
       </c>
       <c r="CG8" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH8" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI8" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ8" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK8" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL8" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM8" s="3" t="n">
@@ -6743,19 +6743,19 @@
         <v>0</v>
       </c>
       <c r="DW8" s="3" t="n">
-        <v>9.779999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="DX8" s="3" t="n">
-        <v>9.35</v>
+        <v>9.25</v>
       </c>
       <c r="DY8" s="3" t="n">
-        <v>7.97</v>
+        <v>7.88</v>
       </c>
       <c r="DZ8" s="3" t="n">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="EA8" s="3" t="n">
-        <v>9.43</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="EB8" s="3" t="n">
         <v>28</v>
@@ -6817,13 +6817,13 @@
         <v>0.1028</v>
       </c>
       <c r="EU8" s="3" t="n">
-        <v>0.0453</v>
+        <v>0.0438</v>
       </c>
       <c r="EV8" s="3" t="n">
         <v>0.0035</v>
       </c>
       <c r="EW8" s="3" t="n">
-        <v>0.0409</v>
+        <v>0.0395</v>
       </c>
       <c r="EX8" s="3" t="n">
         <v>0.1489</v>
@@ -6861,19 +6861,19 @@
         </is>
       </c>
       <c r="FI8" s="3" t="n">
-        <v>7.4</v>
+        <v>7.37</v>
       </c>
       <c r="FJ8" s="3" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="FK8" s="3" t="n">
-        <v>11.02</v>
+        <v>11.07</v>
       </c>
       <c r="FL8" s="3" t="n">
-        <v>18.11</v>
+        <v>18.28</v>
       </c>
       <c r="FM8" s="3" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="FN8" s="3" t="n">
         <v>0</v>
@@ -6884,85 +6884,85 @@
         </is>
       </c>
       <c r="FP8" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="FQ8" s="3" t="n">
-        <v>63.1</v>
+        <v>61.9</v>
       </c>
       <c r="FR8" s="3" t="n">
-        <v>63.1</v>
+        <v>61.9</v>
       </c>
       <c r="FS8" s="3" t="n">
-        <v>55.7</v>
+        <v>54.9</v>
       </c>
       <c r="FT8" s="3" t="n">
-        <v>55.7</v>
+        <v>54.9</v>
       </c>
       <c r="FU8" s="3" t="n">
-        <v>46.7</v>
+        <v>45.7</v>
       </c>
       <c r="FV8" s="3" t="n">
-        <v>46.7</v>
+        <v>45.7</v>
       </c>
       <c r="FW8" s="3" t="n">
-        <v>43</v>
+        <v>41.7</v>
       </c>
       <c r="FX8" s="3" t="n">
-        <v>43</v>
+        <v>41.7</v>
       </c>
       <c r="FY8" s="3" t="n">
-        <v>35.9</v>
+        <v>34.7</v>
       </c>
       <c r="FZ8" s="3" t="n">
-        <v>35.9</v>
+        <v>34.7</v>
       </c>
       <c r="GA8" s="3" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="GB8" s="3" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="GC8" s="3" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="GD8" s="3" t="n">
-        <v>28.1</v>
+        <v>27.6</v>
       </c>
       <c r="GE8" s="3" t="n">
-        <v>28.1</v>
+        <v>27.6</v>
       </c>
       <c r="GF8" s="3" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="GG8" s="3" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="GH8" s="3" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="GI8" s="3" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="GJ8" s="3" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="GK8" s="3" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="GL8" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="GM8" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="GN8" s="3" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="GO8" s="3" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="GP8" s="3" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="GQ8" s="3" t="n">
         <v>8</v>
@@ -7091,16 +7091,16 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>8.09</v>
+        <v>8.01</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>6.52</v>
+        <v>6.39</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>6.52</v>
+        <v>6.39</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>9.220000000000001</v>
@@ -7109,13 +7109,13 @@
         <v>8.16</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>6.85</v>
+        <v>6.84</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7.84</v>
+        <v>7.83</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1.192</v>
+        <v>1.193</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>4.4</v>
@@ -7142,88 +7142,88 @@
         </is>
       </c>
       <c r="X9" s="5" t="n">
-        <v>64</v>
+        <v>62.9</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z9" s="5" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="AA9" s="5" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="AB9" s="6" t="n">
-        <v>46.9</v>
+        <v>62.9</v>
+      </c>
+      <c r="Z9" s="6" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AA9" s="7" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="AB9" s="7" t="n">
+        <v>45.8</v>
       </c>
       <c r="AC9" s="7" t="n">
-        <v>45.9</v>
+        <v>44.8</v>
       </c>
       <c r="AD9" s="7" t="n">
-        <v>45.4</v>
+        <v>44.3</v>
       </c>
       <c r="AE9" s="7" t="n">
-        <v>41.4</v>
+        <v>40.6</v>
       </c>
       <c r="AF9" s="7" t="n">
-        <v>40.9</v>
+        <v>40.1</v>
       </c>
       <c r="AG9" s="8" t="n">
-        <v>33.8</v>
+        <v>32.9</v>
       </c>
       <c r="AH9" s="8" t="n">
-        <v>33.3</v>
+        <v>32.4</v>
       </c>
       <c r="AI9" s="8" t="n">
-        <v>28.3</v>
+        <v>27.6</v>
       </c>
       <c r="AJ9" s="8" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="AK9" s="8" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="AL9" s="8" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="AM9" s="8" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="AN9" s="8" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="AO9" s="8" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="AP9" s="8" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="AQ9" s="8" t="n">
-        <v>19.7</v>
+        <v>18.9</v>
       </c>
       <c r="AR9" s="8" t="n">
-        <v>19.7</v>
+        <v>18.9</v>
       </c>
       <c r="AS9" s="8" t="n">
-        <v>17.7</v>
+        <v>17.2</v>
       </c>
       <c r="AT9" s="8" t="n">
-        <v>17.7</v>
+        <v>17.2</v>
       </c>
       <c r="AU9" s="8" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="AV9" s="8" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="AW9" s="8" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="AX9" s="8" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="AY9" s="3" t="n">
-        <v>176.39</v>
+        <v>174.21</v>
       </c>
       <c r="AZ9" s="4" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="BA9" s="9" t="inlineStr">
         <is>
-          <t>MORE 4.0 | 58.2% | Edge +2.5</t>
+          <t>MORE 3.0 | 62.9% | Edge +3.4</t>
         </is>
       </c>
       <c r="BB9" s="4" t="inlineStr">
@@ -7241,20 +7241,20 @@
         </is>
       </c>
       <c r="BC9" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD9" s="3" t="n">
-        <v>58.2</v>
+        <v>62.9</v>
       </c>
       <c r="BE9" s="3" t="n">
-        <v>2.52</v>
+        <v>3.39</v>
       </c>
       <c r="BF9" s="3" t="n">
-        <v>16.4</v>
+        <v>25.8</v>
       </c>
       <c r="BG9" s="4" t="inlineStr">
         <is>
-          <t>Playable</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="BH9" s="3" t="n">
@@ -7345,23 +7345,23 @@
         <v>1.04</v>
       </c>
       <c r="CG9" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH9" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI9" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ9" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK9" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL9" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM9" s="3" t="n">
@@ -7483,19 +7483,19 @@
         <v>0</v>
       </c>
       <c r="DW9" s="3" t="n">
-        <v>8.710000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DX9" s="3" t="n">
-        <v>8.42</v>
+        <v>8.33</v>
       </c>
       <c r="DY9" s="3" t="n">
-        <v>7.74</v>
+        <v>7.66</v>
       </c>
       <c r="DZ9" s="3" t="n">
-        <v>7.37</v>
+        <v>7.3</v>
       </c>
       <c r="EA9" s="3" t="n">
-        <v>7.87</v>
+        <v>7.78</v>
       </c>
       <c r="EB9" s="3" t="n">
         <v>28</v>
@@ -7557,13 +7557,13 @@
         <v>0.1272</v>
       </c>
       <c r="EU9" s="3" t="n">
-        <v>0.0344</v>
+        <v>0.0333</v>
       </c>
       <c r="EV9" s="3" t="n">
         <v>0.0029</v>
       </c>
       <c r="EW9" s="3" t="n">
-        <v>0.0342</v>
+        <v>0.033</v>
       </c>
       <c r="EX9" s="3" t="n">
         <v>0.0956</v>
@@ -7601,19 +7601,19 @@
         </is>
       </c>
       <c r="FI9" s="3" t="n">
-        <v>7.84</v>
+        <v>7.83</v>
       </c>
       <c r="FJ9" s="3" t="n">
         <v>0.78</v>
       </c>
       <c r="FK9" s="3" t="n">
-        <v>9.119999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="FL9" s="3" t="n">
-        <v>18.66</v>
+        <v>17.48</v>
       </c>
       <c r="FM9" s="3" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="FN9" s="3" t="n">
         <v>0</v>
@@ -7624,85 +7624,85 @@
         </is>
       </c>
       <c r="FP9" s="3" t="n">
-        <v>56</v>
+        <v>54.9</v>
       </c>
       <c r="FQ9" s="3" t="n">
-        <v>56</v>
+        <v>54.9</v>
       </c>
       <c r="FR9" s="3" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="FS9" s="3" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="FT9" s="3" t="n">
-        <v>40.9</v>
+        <v>39.8</v>
       </c>
       <c r="FU9" s="3" t="n">
-        <v>40.9</v>
+        <v>39.8</v>
       </c>
       <c r="FV9" s="3" t="n">
-        <v>40.9</v>
+        <v>39.8</v>
       </c>
       <c r="FW9" s="3" t="n">
-        <v>37.4</v>
+        <v>36.6</v>
       </c>
       <c r="FX9" s="3" t="n">
-        <v>37.4</v>
+        <v>36.6</v>
       </c>
       <c r="FY9" s="3" t="n">
-        <v>30.8</v>
+        <v>29.9</v>
       </c>
       <c r="FZ9" s="3" t="n">
-        <v>30.8</v>
+        <v>29.9</v>
       </c>
       <c r="GA9" s="3" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="GB9" s="3" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="GC9" s="3" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="GD9" s="3" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="GE9" s="3" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="GF9" s="3" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="GG9" s="3" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="GH9" s="3" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="GI9" s="3" t="n">
-        <v>19.7</v>
+        <v>18.9</v>
       </c>
       <c r="GJ9" s="3" t="n">
-        <v>19.7</v>
+        <v>18.9</v>
       </c>
       <c r="GK9" s="3" t="n">
-        <v>17.7</v>
+        <v>17.2</v>
       </c>
       <c r="GL9" s="3" t="n">
-        <v>17.7</v>
+        <v>17.2</v>
       </c>
       <c r="GM9" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="GN9" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="GO9" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="GP9" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="GQ9" s="3" t="n">
         <v>8</v>
@@ -7831,16 +7831,16 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>7.86</v>
+        <v>7.78</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>4.04</v>
+        <v>5.03</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>6.38</v>
@@ -7849,13 +7849,13 @@
         <v>6.24</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>6.24</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.98</v>
+        <v>0.975</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>3.6</v>
@@ -7882,88 +7882,88 @@
         </is>
       </c>
       <c r="X10" s="5" t="n">
-        <v>73.7</v>
+        <v>74.2</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>73.7</v>
+        <v>74.2</v>
       </c>
       <c r="Z10" s="5" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="AA10" s="5" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
       <c r="AB10" s="6" t="n">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
       <c r="AC10" s="7" t="n">
-        <v>54.9</v>
+        <v>55.2</v>
       </c>
       <c r="AD10" s="7" t="n">
-        <v>44.5</v>
+        <v>43.9</v>
       </c>
       <c r="AE10" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF10" s="7" t="n">
-        <v>40.1</v>
+        <v>43.4</v>
+      </c>
+      <c r="AF10" s="8" t="n">
+        <v>39.6</v>
       </c>
       <c r="AG10" s="8" t="n">
-        <v>33</v>
+        <v>32.3</v>
       </c>
       <c r="AH10" s="8" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="AI10" s="8" t="n">
-        <v>27.1</v>
+        <v>26.4</v>
       </c>
       <c r="AJ10" s="8" t="n">
-        <v>26.1</v>
+        <v>25.4</v>
       </c>
       <c r="AK10" s="8" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="AL10" s="8" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="AM10" s="8" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="AN10" s="8" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="AO10" s="8" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="AP10" s="8" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="AQ10" s="8" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="AR10" s="8" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="AS10" s="8" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="AT10" s="8" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="AU10" s="8" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="AV10" s="8" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="AW10" s="8" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="AX10" s="8" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="AY10" s="3" t="n">
-        <v>174.6</v>
+        <v>174.16</v>
       </c>
       <c r="AZ10" s="4" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="BA10" s="9" t="inlineStr">
         <is>
-          <t>MORE 4.0 | 62.4% | Edge +2.1</t>
+          <t>MORE 4.0 | 62.3% | Edge +2.1</t>
         </is>
       </c>
       <c r="BB10" s="4" t="inlineStr">
@@ -7984,13 +7984,13 @@
         <v>4</v>
       </c>
       <c r="BD10" s="3" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
       <c r="BE10" s="3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BF10" s="3" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="BG10" s="4" t="inlineStr">
         <is>
@@ -8085,23 +8085,23 @@
         <v>1.04</v>
       </c>
       <c r="CG10" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH10" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI10" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ10" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK10" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL10" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM10" s="3" t="n">
@@ -8223,19 +8223,19 @@
         <v>0.0159</v>
       </c>
       <c r="DW10" s="3" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="DX10" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="DX10" s="3" t="n">
-        <v>8.17</v>
-      </c>
       <c r="DY10" s="3" t="n">
-        <v>8.550000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ10" s="3" t="n">
-        <v>7.54</v>
+        <v>7.47</v>
       </c>
       <c r="EA10" s="3" t="n">
-        <v>6.84</v>
+        <v>6.76</v>
       </c>
       <c r="EB10" s="3" t="n">
         <v>28</v>
@@ -8297,13 +8297,13 @@
         <v>0.1199</v>
       </c>
       <c r="EU10" s="3" t="n">
-        <v>0.0353</v>
+        <v>0.0341</v>
       </c>
       <c r="EV10" s="3" t="n">
         <v>0.0023</v>
       </c>
       <c r="EW10" s="3" t="n">
-        <v>0.0266</v>
+        <v>0.0257</v>
       </c>
       <c r="EX10" s="3" t="n">
         <v>0.08690000000000001</v>
@@ -8344,16 +8344,16 @@
         <v>6.24</v>
       </c>
       <c r="FJ10" s="3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="FK10" s="3" t="n">
-        <v>8.94</v>
+        <v>8.93</v>
       </c>
       <c r="FL10" s="3" t="n">
-        <v>15.8</v>
+        <v>15.76</v>
       </c>
       <c r="FM10" s="3" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="FN10" s="3" t="n">
         <v>0</v>
@@ -8364,85 +8364,85 @@
         </is>
       </c>
       <c r="FP10" s="3" t="n">
-        <v>65.7</v>
+        <v>66.2</v>
       </c>
       <c r="FQ10" s="3" t="n">
-        <v>65.7</v>
+        <v>66.2</v>
       </c>
       <c r="FR10" s="3" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="FS10" s="3" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="FT10" s="3" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
       <c r="FU10" s="3" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
       <c r="FV10" s="3" t="n">
-        <v>40</v>
+        <v>39.4</v>
       </c>
       <c r="FW10" s="3" t="n">
-        <v>40</v>
+        <v>39.4</v>
       </c>
       <c r="FX10" s="3" t="n">
-        <v>36.6</v>
+        <v>36.1</v>
       </c>
       <c r="FY10" s="3" t="n">
-        <v>30</v>
+        <v>29.3</v>
       </c>
       <c r="FZ10" s="3" t="n">
-        <v>30</v>
+        <v>29.3</v>
       </c>
       <c r="GA10" s="3" t="n">
-        <v>26.1</v>
+        <v>25.4</v>
       </c>
       <c r="GB10" s="3" t="n">
-        <v>26.1</v>
+        <v>25.4</v>
       </c>
       <c r="GC10" s="3" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="GD10" s="3" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="GE10" s="3" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="GF10" s="3" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="GG10" s="3" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="GH10" s="3" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="GI10" s="3" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="GJ10" s="3" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="GK10" s="3" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="GL10" s="3" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="GM10" s="3" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="GN10" s="3" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="GO10" s="3" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="GP10" s="3" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="GQ10" s="3" t="n">
         <v>8</v>
@@ -8571,13 +8571,13 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>7.09</v>
+        <v>7.01</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.99</v>
+        <v>6.94</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>6.99</v>
+        <v>6.94</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>5.42</v>
@@ -8589,13 +8589,13 @@
         <v>5.42</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>6.88</v>
+        <v>6.92</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>5.42</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.788</v>
+        <v>0.783</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.4</v>
@@ -8622,46 +8622,46 @@
         </is>
       </c>
       <c r="X11" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="Z11" s="5" t="n">
-        <v>79.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="AA11" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AB11" s="5" t="n">
-        <v>66.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>62</v>
+        <v>60.8</v>
       </c>
       <c r="AD11" s="6" t="n">
-        <v>50.3</v>
+        <v>49.5</v>
       </c>
       <c r="AE11" s="7" t="n">
-        <v>49.8</v>
+        <v>49</v>
       </c>
       <c r="AF11" s="7" t="n">
-        <v>46</v>
+        <v>45.3</v>
       </c>
       <c r="AG11" s="8" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="AH11" s="8" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="AI11" s="8" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="AJ11" s="8" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="AK11" s="8" t="n">
-        <v>27.5</v>
+        <v>27.1</v>
       </c>
       <c r="AL11" s="8" t="n">
         <v>23.2</v>
@@ -8670,40 +8670,40 @@
         <v>23.2</v>
       </c>
       <c r="AN11" s="8" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AO11" s="8" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AP11" s="8" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AQ11" s="8" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="AR11" s="8" t="n">
-        <v>17.5</v>
+        <v>14.3</v>
       </c>
       <c r="AS11" s="8" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="AT11" s="8" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="AU11" s="8" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="AV11" s="8" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="AW11" s="8" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="AX11" s="8" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="AY11" s="3" t="n">
-        <v>174.02</v>
+        <v>173.1</v>
       </c>
       <c r="AZ11" s="4" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="BA11" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 62.0% | Edge +2.0</t>
+          <t>MORE 5.0 | 60.8% | Edge +1.9</t>
         </is>
       </c>
       <c r="BB11" s="4" t="inlineStr">
@@ -8724,17 +8724,17 @@
         <v>5</v>
       </c>
       <c r="BD11" s="3" t="n">
-        <v>62</v>
+        <v>60.8</v>
       </c>
       <c r="BE11" s="3" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="BF11" s="3" t="n">
-        <v>24</v>
+        <v>21.6</v>
       </c>
       <c r="BG11" s="4" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Playable</t>
         </is>
       </c>
       <c r="BH11" s="3" t="n">
@@ -8825,23 +8825,23 @@
         <v>1.04</v>
       </c>
       <c r="CG11" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH11" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI11" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ11" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK11" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL11" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM11" s="3" t="n">
@@ -8963,19 +8963,19 @@
         <v>0</v>
       </c>
       <c r="DW11" s="3" t="n">
-        <v>7.24</v>
+        <v>7.15</v>
       </c>
       <c r="DX11" s="3" t="n">
-        <v>6.88</v>
+        <v>6.79</v>
       </c>
       <c r="DY11" s="3" t="n">
-        <v>6.75</v>
+        <v>6.68</v>
       </c>
       <c r="DZ11" s="3" t="n">
-        <v>7.53</v>
+        <v>7.44</v>
       </c>
       <c r="EA11" s="3" t="n">
-        <v>7.06</v>
+        <v>6.96</v>
       </c>
       <c r="EB11" s="3" t="n">
         <v>28</v>
@@ -9037,13 +9037,13 @@
         <v>0.157</v>
       </c>
       <c r="EU11" s="3" t="n">
-        <v>0.0565</v>
+        <v>0.0546</v>
       </c>
       <c r="EV11" s="3" t="n">
         <v>0.0035</v>
       </c>
       <c r="EW11" s="3" t="n">
-        <v>0.0395</v>
+        <v>0.0382</v>
       </c>
       <c r="EX11" s="3" t="n">
         <v>0.0654</v>
@@ -9084,16 +9084,16 @@
         <v>5.42</v>
       </c>
       <c r="FJ11" s="3" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="FK11" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="FL11" s="3" t="n">
-        <v>14.88</v>
+        <v>14.82</v>
       </c>
       <c r="FM11" s="3" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="FN11" s="3" t="n">
         <v>0</v>
@@ -9104,46 +9104,46 @@
         </is>
       </c>
       <c r="FP11" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="FQ11" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="FR11" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="FS11" s="3" t="n">
-        <v>60.6</v>
+        <v>59.1</v>
       </c>
       <c r="FT11" s="3" t="n">
-        <v>60.6</v>
+        <v>59.1</v>
       </c>
       <c r="FU11" s="3" t="n">
-        <v>57</v>
+        <v>55.8</v>
       </c>
       <c r="FV11" s="3" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="FW11" s="3" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="FX11" s="3" t="n">
-        <v>42.5</v>
+        <v>41.8</v>
       </c>
       <c r="FY11" s="3" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="FZ11" s="3" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="GA11" s="3" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="GB11" s="3" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="GC11" s="3" t="n">
-        <v>27.5</v>
+        <v>27.1</v>
       </c>
       <c r="GD11" s="3" t="n">
         <v>23.2</v>
@@ -9152,37 +9152,37 @@
         <v>23.2</v>
       </c>
       <c r="GF11" s="3" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="GG11" s="3" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="GH11" s="3" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="GI11" s="3" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="GJ11" s="3" t="n">
-        <v>17.5</v>
+        <v>14.3</v>
       </c>
       <c r="GK11" s="3" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="GL11" s="3" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="GM11" s="3" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="GN11" s="3" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="GO11" s="3" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="GP11" s="3" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="GQ11" s="3" t="n">
         <v>8</v>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>6.77</v>
+        <v>6.68</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>6.96</v>
@@ -9320,7 +9320,7 @@
         <v>6.96</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>5.6</v>
@@ -9329,13 +9329,13 @@
         <v>5.75</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>7.03</v>
+        <v>7.07</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>5.75</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>5.6</v>
@@ -9362,46 +9362,46 @@
         </is>
       </c>
       <c r="X12" s="5" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="Z12" s="5" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="AA12" s="5" t="n">
-        <v>66.2</v>
+        <v>66</v>
       </c>
       <c r="AB12" s="5" t="n">
-        <v>65.2</v>
+        <v>65</v>
       </c>
       <c r="AC12" s="5" t="n">
         <v>60.7</v>
       </c>
       <c r="AD12" s="6" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="AE12" s="7" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="AF12" s="7" t="n">
         <v>44.6</v>
       </c>
       <c r="AG12" s="8" t="n">
-        <v>37.5</v>
+        <v>37.8</v>
       </c>
       <c r="AH12" s="8" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="AI12" s="8" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="AJ12" s="8" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="AK12" s="8" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="AL12" s="8" t="n">
         <v>23.6</v>
@@ -9410,40 +9410,40 @@
         <v>23.6</v>
       </c>
       <c r="AN12" s="8" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AO12" s="8" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AP12" s="8" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="AQ12" s="8" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="AR12" s="8" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="AS12" s="8" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AT12" s="8" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AU12" s="8" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="AV12" s="8" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="AW12" s="8" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="AX12" s="8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" s="3" t="n">
-        <v>172.78</v>
+        <v>172.74</v>
       </c>
       <c r="AZ12" s="4" t="inlineStr">
         <is>
@@ -9565,23 +9565,23 @@
         <v>1.04</v>
       </c>
       <c r="CG12" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH12" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI12" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ12" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK12" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL12" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM12" s="3" t="n">
@@ -9703,19 +9703,19 @@
         <v>0</v>
       </c>
       <c r="DW12" s="3" t="n">
-        <v>6.9</v>
+        <v>6.81</v>
       </c>
       <c r="DX12" s="3" t="n">
-        <v>7.07</v>
+        <v>6.97</v>
       </c>
       <c r="DY12" s="3" t="n">
-        <v>6.44</v>
+        <v>6.36</v>
       </c>
       <c r="DZ12" s="3" t="n">
-        <v>6.73</v>
+        <v>6.66</v>
       </c>
       <c r="EA12" s="3" t="n">
-        <v>6.71</v>
+        <v>6.62</v>
       </c>
       <c r="EB12" s="3" t="n">
         <v>28</v>
@@ -9777,13 +9777,13 @@
         <v>0.172</v>
       </c>
       <c r="EU12" s="3" t="n">
-        <v>0.048</v>
+        <v>0.0464</v>
       </c>
       <c r="EV12" s="3" t="n">
         <v>0.0034</v>
       </c>
       <c r="EW12" s="3" t="n">
-        <v>0.0467</v>
+        <v>0.0452</v>
       </c>
       <c r="EX12" s="3" t="n">
         <v>0.06710000000000001</v>
@@ -9824,16 +9824,16 @@
         <v>5.75</v>
       </c>
       <c r="FJ12" s="3" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="FK12" s="3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="FL12" s="3" t="n">
-        <v>15.17</v>
+        <v>15.13</v>
       </c>
       <c r="FM12" s="3" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="FN12" s="3" t="n">
         <v>0</v>
@@ -9844,46 +9844,46 @@
         </is>
       </c>
       <c r="FP12" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="FQ12" s="3" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="FR12" s="3" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="FS12" s="3" t="n">
-        <v>59.2</v>
+        <v>59</v>
       </c>
       <c r="FT12" s="3" t="n">
-        <v>59.2</v>
+        <v>59</v>
       </c>
       <c r="FU12" s="3" t="n">
         <v>55.7</v>
       </c>
       <c r="FV12" s="3" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="FW12" s="3" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="FX12" s="3" t="n">
         <v>41.1</v>
       </c>
       <c r="FY12" s="3" t="n">
-        <v>34.5</v>
+        <v>34.8</v>
       </c>
       <c r="FZ12" s="3" t="n">
-        <v>34.5</v>
+        <v>34.8</v>
       </c>
       <c r="GA12" s="3" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="GB12" s="3" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="GC12" s="3" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="GD12" s="3" t="n">
         <v>23.6</v>
@@ -9892,37 +9892,37 @@
         <v>23.6</v>
       </c>
       <c r="GF12" s="3" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="GG12" s="3" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="GH12" s="3" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="GI12" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="GJ12" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="GK12" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="GL12" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="GM12" s="3" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="GN12" s="3" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="GO12" s="3" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="GP12" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="GQ12" s="3" t="n">
         <v>8</v>
@@ -10051,13 +10051,13 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>6.68</v>
+        <v>6.61</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6.38</v>
+        <v>6.32</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>6.38</v>
+        <v>6.32</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>5.31</v>
@@ -10069,13 +10069,13 @@
         <v>5.02</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>6.48</v>
+        <v>6.56</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>5.02</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>0.774</v>
+        <v>0.766</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>9.6</v>
@@ -10102,31 +10102,31 @@
         </is>
       </c>
       <c r="X13" s="5" t="n">
-        <v>84.3</v>
+        <v>83.3</v>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>76.8</v>
+        <v>83.3</v>
       </c>
       <c r="Z13" s="5" t="n">
-        <v>76.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AA13" s="5" t="n">
-        <v>64.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="AC13" s="5" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="AD13" s="6" t="n">
-        <v>46.1</v>
+        <v>62.1</v>
+      </c>
+      <c r="AC13" s="6" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="AD13" s="7" t="n">
+        <v>45.7</v>
       </c>
       <c r="AE13" s="7" t="n">
-        <v>45.6</v>
+        <v>45.2</v>
       </c>
       <c r="AF13" s="7" t="n">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="AG13" s="8" t="n">
         <v>34.4</v>
@@ -10135,55 +10135,55 @@
         <v>33.9</v>
       </c>
       <c r="AI13" s="8" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="AJ13" s="8" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="AK13" s="8" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="AL13" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="AM13" s="8" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AN13" s="8" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AO13" s="8" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="AP13" s="8" t="n">
-        <v>16.3</v>
+        <v>15.3</v>
       </c>
       <c r="AQ13" s="8" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="AR13" s="8" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="AS13" s="8" t="n">
-        <v>12</v>
+        <v>11.1</v>
       </c>
       <c r="AT13" s="8" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="AU13" s="8" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AV13" s="8" t="n">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="AW13" s="8" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" s="8" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="AY13" s="3" t="n">
-        <v>167.81</v>
+        <v>166.83</v>
       </c>
       <c r="AZ13" s="4" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="BA13" s="9" t="inlineStr">
         <is>
-          <t>MORE 5.0 | 58.3% | Edge +1.4</t>
+          <t>MORE 4.5 | 62.1% | Edge +1.8</t>
         </is>
       </c>
       <c r="BB13" s="4" t="inlineStr">
@@ -10201,20 +10201,20 @@
         </is>
       </c>
       <c r="BC13" s="3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" s="3" t="n">
-        <v>58.3</v>
+        <v>62.1</v>
       </c>
       <c r="BE13" s="3" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="BF13" s="3" t="n">
-        <v>16.6</v>
+        <v>24.2</v>
       </c>
       <c r="BG13" s="4" t="inlineStr">
         <is>
-          <t>Playable</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="BH13" s="3" t="n">
@@ -10305,23 +10305,23 @@
         <v>1.04</v>
       </c>
       <c r="CG13" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH13" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI13" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ13" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK13" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL13" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM13" s="3" t="n">
@@ -10443,19 +10443,19 @@
         <v>0.0357</v>
       </c>
       <c r="DW13" s="3" t="n">
-        <v>6.46</v>
+        <v>6.39</v>
       </c>
       <c r="DX13" s="3" t="n">
-        <v>6.3</v>
+        <v>6.23</v>
       </c>
       <c r="DY13" s="3" t="n">
-        <v>7.33</v>
+        <v>7.24</v>
       </c>
       <c r="DZ13" s="3" t="n">
-        <v>7.42</v>
+        <v>7.34</v>
       </c>
       <c r="EA13" s="3" t="n">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="EB13" s="3" t="n">
         <v>28</v>
@@ -10517,13 +10517,13 @@
         <v>0.1516</v>
       </c>
       <c r="EU13" s="3" t="n">
-        <v>0.0519</v>
+        <v>0.0502</v>
       </c>
       <c r="EV13" s="3" t="n">
         <v>0.0039</v>
       </c>
       <c r="EW13" s="3" t="n">
-        <v>0.0318</v>
+        <v>0.0308</v>
       </c>
       <c r="EX13" s="3" t="n">
         <v>0.0751</v>
@@ -10564,16 +10564,16 @@
         <v>5.02</v>
       </c>
       <c r="FJ13" s="3" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="FK13" s="3" t="n">
-        <v>8.41</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="FL13" s="3" t="n">
-        <v>13.83</v>
+        <v>13.73</v>
       </c>
       <c r="FM13" s="3" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="FN13" s="3" t="n">
         <v>0</v>
@@ -10584,31 +10584,31 @@
         </is>
       </c>
       <c r="FP13" s="3" t="n">
-        <v>76.3</v>
+        <v>75.3</v>
       </c>
       <c r="FQ13" s="3" t="n">
-        <v>68.8</v>
+        <v>75.3</v>
       </c>
       <c r="FR13" s="3" t="n">
-        <v>68.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="FS13" s="3" t="n">
-        <v>57.4</v>
+        <v>56.1</v>
       </c>
       <c r="FT13" s="3" t="n">
-        <v>57.4</v>
+        <v>56.1</v>
       </c>
       <c r="FU13" s="3" t="n">
-        <v>53.3</v>
+        <v>52.2</v>
       </c>
       <c r="FV13" s="3" t="n">
-        <v>41.6</v>
+        <v>41.2</v>
       </c>
       <c r="FW13" s="3" t="n">
-        <v>41.6</v>
+        <v>41.2</v>
       </c>
       <c r="FX13" s="3" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="FY13" s="3" t="n">
         <v>31.4</v>
@@ -10617,52 +10617,52 @@
         <v>31.4</v>
       </c>
       <c r="GA13" s="3" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="GB13" s="3" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="GC13" s="3" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="GD13" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="GE13" s="3" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="GF13" s="3" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="GG13" s="3" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="GH13" s="3" t="n">
-        <v>16.3</v>
+        <v>15.3</v>
       </c>
       <c r="GI13" s="3" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="GJ13" s="3" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="GK13" s="3" t="n">
-        <v>12</v>
+        <v>11.1</v>
       </c>
       <c r="GL13" s="3" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="GM13" s="3" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="GN13" s="3" t="n">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="GO13" s="3" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="GP13" s="3" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="GQ13" s="3" t="n">
         <v>8</v>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -10787,143 +10787,143 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="R14" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>1.068</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>2.8</v>
-      </c>
       <c r="S14" s="3" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>6.13</v>
+        <v>6.2</v>
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>5|0|2|2|5</t>
+          <t>10|13|2|5|4</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>5|0|2|2|5|2|7|2|23|5</t>
+          <t>10|13|2|5|4|0|8|15|5|3</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>5|0|2|2|5|2|7|2|23|5|20|5|0|14|0</t>
+          <t>10|13|2|5|4|0|8|15|5|3|8|10|5|3|2</t>
         </is>
       </c>
       <c r="X14" s="5" t="n">
-        <v>69.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>59.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="AA14" s="6" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="AB14" s="7" t="n">
-        <v>51.8</v>
+        <v>59.6</v>
+      </c>
+      <c r="AA14" s="5" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="AB14" s="6" t="n">
+        <v>52.6</v>
       </c>
       <c r="AC14" s="7" t="n">
-        <v>40.9</v>
+        <v>51.6</v>
       </c>
       <c r="AD14" s="7" t="n">
         <v>40.4</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="AF14" s="8" t="n">
-        <v>36.5</v>
+        <v>36.1</v>
       </c>
       <c r="AG14" s="8" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="AH14" s="8" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="AI14" s="8" t="n">
-        <v>27</v>
+        <v>23.3</v>
       </c>
       <c r="AJ14" s="8" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="AK14" s="8" t="n">
-        <v>22.9</v>
+        <v>19</v>
       </c>
       <c r="AL14" s="8" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="AM14" s="8" t="n">
-        <v>19.6</v>
+        <v>15.8</v>
       </c>
       <c r="AN14" s="8" t="n">
-        <v>17.1</v>
+        <v>15.8</v>
       </c>
       <c r="AO14" s="8" t="n">
-        <v>17.1</v>
+        <v>14.2</v>
       </c>
       <c r="AP14" s="8" t="n">
-        <v>15.5</v>
+        <v>14.2</v>
       </c>
       <c r="AQ14" s="8" t="n">
-        <v>15.5</v>
+        <v>12.4</v>
       </c>
       <c r="AR14" s="8" t="n">
-        <v>13.9</v>
+        <v>11.5</v>
       </c>
       <c r="AS14" s="8" t="n">
-        <v>13.9</v>
+        <v>11.5</v>
       </c>
       <c r="AT14" s="8" t="n">
-        <v>13.1</v>
+        <v>8.9</v>
       </c>
       <c r="AU14" s="8" t="n">
-        <v>13.1</v>
+        <v>8.9</v>
       </c>
       <c r="AV14" s="8" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW14" s="8" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" s="8" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AY14" s="3" t="n">
-        <v>157.19</v>
+        <v>154.48</v>
       </c>
       <c r="AZ14" s="4" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="BA14" s="9" t="inlineStr">
         <is>
-          <t>MORE 3.5 | 59.3% | Edge +2.2</t>
+          <t>MORE 4.0 | 59.1% | Edge +1.5</t>
         </is>
       </c>
       <c r="BB14" s="4" t="inlineStr">
@@ -10941,16 +10941,16 @@
         </is>
       </c>
       <c r="BC14" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BD14" s="3" t="n">
-        <v>59.3</v>
+        <v>59.1</v>
       </c>
       <c r="BE14" s="3" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="BF14" s="3" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="BG14" s="4" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         </is>
       </c>
       <c r="BH14" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BI14" s="4" t="inlineStr">
         <is>
@@ -10966,27 +10966,27 @@
         </is>
       </c>
       <c r="BJ14" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BK14" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BL14" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>4-5-5-5-5-4-4</t>
+          <t>9-6-6-6-4-7-7</t>
         </is>
       </c>
       <c r="BN14" s="3" t="n">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="BO14" s="3" t="n">
         <v>100</v>
       </c>
       <c r="BP14" s="3" t="n">
-        <v>4.61</v>
+        <v>4.4</v>
       </c>
       <c r="BQ14" s="4" t="inlineStr">
         <is>
@@ -11045,89 +11045,89 @@
         <v>1.04</v>
       </c>
       <c r="CG14" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH14" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI14" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ14" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK14" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL14" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM14" s="3" t="n">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="CN14" s="3" t="n">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="CO14" s="3" t="n">
-        <v>0.215</v>
+        <v>0.249</v>
       </c>
       <c r="CP14" s="3" t="n">
-        <v>0.278</v>
+        <v>0.308</v>
       </c>
       <c r="CQ14" s="3" t="n">
-        <v>0.354</v>
+        <v>0.393</v>
       </c>
       <c r="CR14" s="3" t="n">
-        <v>0.632</v>
+        <v>0.701</v>
       </c>
       <c r="CS14" s="3" t="n">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="CT14" s="3" t="n">
-        <v>0.644</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="CU14" s="3" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="CV14" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CW14" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CX14" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CY14" s="3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="CZ14" s="3" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="DA14" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DB14" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="DC14" s="3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="DD14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Detroit Tigers: 5 FS|2026-07-11 @ Detroit Tigers: 0 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 2 FS|2026-07-08 @ Cincinnati Reds: 5 FS</t>
+          <t>2026-07-12 @ Detroit Tigers: 10 FS|2026-07-11 @ Detroit Tigers: 13 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 5 FS|2026-07-08 @ Cincinnati Reds: 4 FS</t>
         </is>
       </c>
       <c r="DE14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Detroit Tigers: 5 FS|2026-07-11 @ Detroit Tigers: 0 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 2 FS|2026-07-08 @ Cincinnati Reds: 5 FS|2026-07-07 @ Cincinnati Reds: 2 FS|2026-07-06 @ Kansas City Royals: 7 FS|2026-07-05 @ Kansas City Royals: 2 FS|2026-07-04 @ Kansas City Royals: 23 FS|2026-07-02 vs Pittsburgh Pirates: 5 FS</t>
+          <t>2026-07-12 @ Detroit Tigers: 10 FS|2026-07-11 @ Detroit Tigers: 13 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 5 FS|2026-07-08 @ Cincinnati Reds: 4 FS|2026-07-07 @ Cincinnati Reds: 0 FS|2026-07-06 @ Kansas City Royals: 8 FS|2026-07-05 @ Kansas City Royals: 15 FS|2026-07-04 @ Kansas City Royals: 5 FS|2026-07-02 vs Pittsburgh Pirates: 3 FS</t>
         </is>
       </c>
       <c r="DF14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Detroit Tigers: 5 FS|2026-07-11 @ Detroit Tigers: 0 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 2 FS|2026-07-08 @ Cincinnati Reds: 5 FS|2026-07-07 @ Cincinnati Reds: 2 FS|2026-07-06 @ Kansas City Royals: 7 FS|2026-07-05 @ Kansas City Royals: 2 FS|2026-07-04 @ Kansas City Royals: 23 FS|2026-07-02 vs Pittsburgh Pirates: 5 FS|2026-07-01 vs Pittsburgh Pirates: 20 FS|2026-06-30 vs Pittsburgh Pirates: 5 FS|2026-06-29 vs Pittsburgh Pirates: 0 FS|2026-06-28 @ New York Mets: 14 FS|2026-06-26 @ New York Mets: 0 FS</t>
+          <t>2026-07-12 @ Detroit Tigers: 10 FS|2026-07-11 @ Detroit Tigers: 13 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 5 FS|2026-07-08 @ Cincinnati Reds: 4 FS|2026-07-07 @ Cincinnati Reds: 0 FS|2026-07-06 @ Kansas City Royals: 8 FS|2026-07-05 @ Kansas City Royals: 15 FS|2026-07-04 @ Kansas City Royals: 5 FS|2026-07-02 vs Pittsburgh Pirates: 3 FS|2026-07-01 vs Pittsburgh Pirates: 8 FS|2026-06-30 vs Pittsburgh Pirates: 10 FS|2026-06-29 vs Pittsburgh Pirates: 5 FS|2026-06-28 @ New York Mets: 3 FS|2026-06-27 @ New York Mets: 2 FS</t>
         </is>
       </c>
       <c r="DG14" s="3" t="n">
@@ -11137,10 +11137,10 @@
         <v>30</v>
       </c>
       <c r="DI14" s="3" t="n">
-        <v>6.07</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DJ14" s="3" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="DK14" s="4" t="inlineStr">
         <is>
@@ -11148,54 +11148,54 @@
         </is>
       </c>
       <c r="DL14" s="3" t="n">
-        <v>3.29</v>
+        <v>6</v>
       </c>
       <c r="DM14" s="3" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="DN14" s="3" t="n">
-        <v>0.189</v>
+        <v>0.315</v>
       </c>
       <c r="DO14" s="4" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="DP14" s="3" t="n">
-        <v>6.07</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DQ14" s="3" t="n">
-        <v>1.508</v>
+        <v>1.542</v>
       </c>
       <c r="DR14" s="3" t="n">
-        <v>0.1639</v>
+        <v>0.2881</v>
       </c>
       <c r="DS14" s="3" t="n">
-        <v>0.0984</v>
+        <v>0.0508</v>
       </c>
       <c r="DT14" s="3" t="n">
-        <v>0.0328</v>
+        <v>0</v>
       </c>
       <c r="DU14" s="3" t="n">
-        <v>0.082</v>
+        <v>0.0678</v>
       </c>
       <c r="DV14" s="3" t="n">
-        <v>0</v>
+        <v>0.0169</v>
       </c>
       <c r="DW14" s="3" t="n">
-        <v>6.86</v>
+        <v>7.11</v>
       </c>
       <c r="DX14" s="3" t="n">
-        <v>6.93</v>
+        <v>7.35</v>
       </c>
       <c r="DY14" s="3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="DZ14" s="3" t="n">
-        <v>6.56</v>
+        <v>6.69</v>
       </c>
       <c r="EA14" s="3" t="n">
-        <v>6.38</v>
+        <v>6.06</v>
       </c>
       <c r="EB14" s="3" t="n">
         <v>28</v>
@@ -11213,25 +11213,25 @@
         <v>20</v>
       </c>
       <c r="EG14" s="3" t="n">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="EH14" s="3" t="n">
-        <v>84.48</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="EI14" s="3" t="n">
-        <v>25.08</v>
+        <v>23.84</v>
       </c>
       <c r="EJ14" s="3" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="EK14" s="3" t="n">
-        <v>32.78</v>
+        <v>29.18</v>
       </c>
       <c r="EL14" s="3" t="n">
-        <v>0.346</v>
+        <v>0.365</v>
       </c>
       <c r="EM14" s="3" t="n">
-        <v>0.9054</v>
+        <v>0.9053</v>
       </c>
       <c r="EN14" s="3" t="n">
         <v>1</v>
@@ -11243,10 +11243,10 @@
         <v>1</v>
       </c>
       <c r="EQ14" s="3" t="n">
-        <v>0.9836</v>
+        <v>1.01</v>
       </c>
       <c r="ER14" s="3" t="n">
-        <v>443</v>
+        <v>532</v>
       </c>
       <c r="ES14" s="4" t="inlineStr">
         <is>
@@ -11254,43 +11254,43 @@
         </is>
       </c>
       <c r="ET14" s="3" t="n">
-        <v>0.1023</v>
+        <v>0.1239</v>
       </c>
       <c r="EU14" s="3" t="n">
-        <v>0.0366</v>
+        <v>0.0388</v>
       </c>
       <c r="EV14" s="3" t="n">
-        <v>0.0023</v>
+        <v>0.0058</v>
       </c>
       <c r="EW14" s="3" t="n">
-        <v>0.0269</v>
+        <v>0.0206</v>
       </c>
       <c r="EX14" s="3" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0992</v>
       </c>
       <c r="EY14" s="3" t="n">
-        <v>0.021</v>
+        <v>0.0107</v>
       </c>
       <c r="EZ14" s="3" t="n">
-        <v>0.1931</v>
+        <v>0.2074</v>
       </c>
       <c r="FA14" s="3" t="n">
-        <v>0.4901</v>
+        <v>0.4317</v>
       </c>
       <c r="FB14" s="3" t="n">
-        <v>0.2517</v>
+        <v>0.331</v>
       </c>
       <c r="FC14" s="3" t="n">
-        <v>0.2582</v>
+        <v>0.2374</v>
       </c>
       <c r="FD14" s="3" t="n">
-        <v>0.0925</v>
+        <v>0.0953</v>
       </c>
       <c r="FE14" s="3" t="n">
-        <v>0.1197</v>
+        <v>0.1053</v>
       </c>
       <c r="FF14" s="3" t="n">
-        <v>0.0083</v>
+        <v>0.0199</v>
       </c>
       <c r="FG14" s="3" t="n">
         <v>1</v>
@@ -11301,19 +11301,19 @@
         </is>
       </c>
       <c r="FI14" s="3" t="n">
-        <v>6.51</v>
+        <v>5.43</v>
       </c>
       <c r="FJ14" s="3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="FK14" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>7.81</v>
       </c>
       <c r="FL14" s="3" t="n">
-        <v>14.44</v>
+        <v>13.35</v>
       </c>
       <c r="FM14" s="3" t="n">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="FN14" s="3" t="n">
         <v>0</v>
@@ -11324,85 +11324,85 @@
         </is>
       </c>
       <c r="FP14" s="3" t="n">
-        <v>61.7</v>
+        <v>63.4</v>
       </c>
       <c r="FQ14" s="3" t="n">
-        <v>51.8</v>
+        <v>63.4</v>
       </c>
       <c r="FR14" s="3" t="n">
-        <v>51.8</v>
+        <v>52.1</v>
       </c>
       <c r="FS14" s="3" t="n">
-        <v>45.8</v>
+        <v>52.1</v>
       </c>
       <c r="FT14" s="3" t="n">
-        <v>45.8</v>
+        <v>46.6</v>
       </c>
       <c r="FU14" s="3" t="n">
-        <v>35.9</v>
+        <v>46.6</v>
       </c>
       <c r="FV14" s="3" t="n">
         <v>35.9</v>
       </c>
       <c r="FW14" s="3" t="n">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="FX14" s="3" t="n">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="FY14" s="3" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="FZ14" s="3" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="GA14" s="3" t="n">
-        <v>26</v>
+        <v>22.3</v>
       </c>
       <c r="GB14" s="3" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="GC14" s="3" t="n">
-        <v>22.9</v>
+        <v>19</v>
       </c>
       <c r="GD14" s="3" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="GE14" s="3" t="n">
-        <v>19.6</v>
+        <v>15.8</v>
       </c>
       <c r="GF14" s="3" t="n">
-        <v>17.1</v>
+        <v>15.8</v>
       </c>
       <c r="GG14" s="3" t="n">
-        <v>17.1</v>
+        <v>14.2</v>
       </c>
       <c r="GH14" s="3" t="n">
-        <v>15.5</v>
+        <v>14.2</v>
       </c>
       <c r="GI14" s="3" t="n">
-        <v>15.5</v>
+        <v>12.4</v>
       </c>
       <c r="GJ14" s="3" t="n">
-        <v>13.9</v>
+        <v>11.5</v>
       </c>
       <c r="GK14" s="3" t="n">
-        <v>13.9</v>
+        <v>11.5</v>
       </c>
       <c r="GL14" s="3" t="n">
-        <v>13.1</v>
+        <v>8.9</v>
       </c>
       <c r="GM14" s="3" t="n">
-        <v>13.1</v>
+        <v>8.9</v>
       </c>
       <c r="GN14" s="3" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="GO14" s="3" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="GP14" s="3" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="GQ14" s="3" t="n">
         <v>8</v>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -11527,143 +11527,143 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>6.83</v>
+        <v>6.73</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.64</v>
+        <v>5.46</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.64</v>
+        <v>5.46</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>4.13</v>
+        <v>3.7</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>5.07</v>
+        <v>6.98</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5.43</v>
+        <v>6.63</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>5.88</v>
+        <v>6.09</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>5.43</v>
+        <v>6.48</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>0.923</v>
+        <v>1.088</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>6.2</v>
+        <v>6.13</v>
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>10|13|2|5|4</t>
+          <t>5|0|2|2|5</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>10|13|2|5|4|0|8|15|5|3</t>
+          <t>5|0|2|2|5|2|7|2|23|5</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>10|13|2|5|4|0|8|15|5|3|8|10|5|3|2</t>
+          <t>5|0|2|2|5|2|7|2|23|5|20|5|0|14|0</t>
         </is>
       </c>
       <c r="X15" s="5" t="n">
-        <v>72.8</v>
+        <v>68</v>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="Z15" s="5" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="AA15" s="5" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="AB15" s="6" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="AC15" s="7" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="AD15" s="7" t="n">
-        <v>41.9</v>
+        <v>58.2</v>
+      </c>
+      <c r="Z15" s="6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="AA15" s="7" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="AB15" s="7" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="AC15" s="8" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="AD15" s="8" t="n">
+        <v>38.6</v>
       </c>
       <c r="AE15" s="8" t="n">
-        <v>38.3</v>
+        <v>35.6</v>
       </c>
       <c r="AF15" s="8" t="n">
-        <v>37.8</v>
+        <v>35.1</v>
       </c>
       <c r="AG15" s="8" t="n">
-        <v>29.8</v>
+        <v>27.8</v>
       </c>
       <c r="AH15" s="8" t="n">
-        <v>29.3</v>
+        <v>27.3</v>
       </c>
       <c r="AI15" s="8" t="n">
-        <v>24.1</v>
+        <v>25.8</v>
       </c>
       <c r="AJ15" s="8" t="n">
-        <v>23.1</v>
+        <v>22.2</v>
       </c>
       <c r="AK15" s="8" t="n">
-        <v>19.6</v>
+        <v>22.2</v>
       </c>
       <c r="AL15" s="8" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="AM15" s="8" t="n">
-        <v>16.3</v>
+        <v>18.8</v>
       </c>
       <c r="AN15" s="8" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="AO15" s="8" t="n">
-        <v>14.3</v>
+        <v>16.5</v>
       </c>
       <c r="AP15" s="8" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="AQ15" s="8" t="n">
-        <v>12.3</v>
+        <v>15</v>
       </c>
       <c r="AR15" s="8" t="n">
-        <v>11.3</v>
+        <v>13.4</v>
       </c>
       <c r="AS15" s="8" t="n">
-        <v>11.3</v>
+        <v>13.4</v>
       </c>
       <c r="AT15" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="AU15" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="AV15" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="AW15" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX15" s="8" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" s="3" t="n">
-        <v>156.64</v>
+        <v>154.06</v>
       </c>
       <c r="AZ15" s="4" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="BA15" s="9" t="inlineStr">
         <is>
-          <t>MORE 4.0 | 60.7% | Edge +1.6</t>
+          <t>MORE 3.0 | 58.2% | Edge +2.5</t>
         </is>
       </c>
       <c r="BB15" s="4" t="inlineStr">
@@ -11681,16 +11681,16 @@
         </is>
       </c>
       <c r="BC15" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD15" s="3" t="n">
-        <v>60.7</v>
+        <v>58.2</v>
       </c>
       <c r="BE15" s="3" t="n">
-        <v>1.64</v>
+        <v>2.46</v>
       </c>
       <c r="BF15" s="3" t="n">
-        <v>21.4</v>
+        <v>16.4</v>
       </c>
       <c r="BG15" s="4" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="BH15" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BI15" s="4" t="inlineStr">
         <is>
@@ -11706,27 +11706,27 @@
         </is>
       </c>
       <c r="BJ15" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BK15" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BL15" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>9-6-6-6-4-7-7</t>
+          <t>4-5-5-5-5-4-4</t>
         </is>
       </c>
       <c r="BN15" s="3" t="n">
-        <v>42.9</v>
+        <v>57.1</v>
       </c>
       <c r="BO15" s="3" t="n">
         <v>100</v>
       </c>
       <c r="BP15" s="3" t="n">
-        <v>4.4</v>
+        <v>4.61</v>
       </c>
       <c r="BQ15" s="4" t="inlineStr">
         <is>
@@ -11785,89 +11785,89 @@
         <v>1.04</v>
       </c>
       <c r="CG15" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH15" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI15" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ15" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK15" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL15" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM15" s="3" t="n">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="CN15" s="3" t="n">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="CO15" s="3" t="n">
-        <v>0.249</v>
+        <v>0.215</v>
       </c>
       <c r="CP15" s="3" t="n">
-        <v>0.308</v>
+        <v>0.278</v>
       </c>
       <c r="CQ15" s="3" t="n">
-        <v>0.393</v>
+        <v>0.354</v>
       </c>
       <c r="CR15" s="3" t="n">
-        <v>0.701</v>
+        <v>0.632</v>
       </c>
       <c r="CS15" s="3" t="n">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="CT15" s="3" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.644</v>
       </c>
       <c r="CU15" s="3" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="CV15" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="CW15" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CX15" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CY15" s="3" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="CZ15" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="DA15" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="DB15" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="DC15" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="DD15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Detroit Tigers: 10 FS|2026-07-11 @ Detroit Tigers: 13 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 5 FS|2026-07-08 @ Cincinnati Reds: 4 FS</t>
+          <t>2026-07-12 @ Detroit Tigers: 5 FS|2026-07-11 @ Detroit Tigers: 0 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 2 FS|2026-07-08 @ Cincinnati Reds: 5 FS</t>
         </is>
       </c>
       <c r="DE15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Detroit Tigers: 10 FS|2026-07-11 @ Detroit Tigers: 13 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 5 FS|2026-07-08 @ Cincinnati Reds: 4 FS|2026-07-07 @ Cincinnati Reds: 0 FS|2026-07-06 @ Kansas City Royals: 8 FS|2026-07-05 @ Kansas City Royals: 15 FS|2026-07-04 @ Kansas City Royals: 5 FS|2026-07-02 vs Pittsburgh Pirates: 3 FS</t>
+          <t>2026-07-12 @ Detroit Tigers: 5 FS|2026-07-11 @ Detroit Tigers: 0 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 2 FS|2026-07-08 @ Cincinnati Reds: 5 FS|2026-07-07 @ Cincinnati Reds: 2 FS|2026-07-06 @ Kansas City Royals: 7 FS|2026-07-05 @ Kansas City Royals: 2 FS|2026-07-04 @ Kansas City Royals: 23 FS|2026-07-02 vs Pittsburgh Pirates: 5 FS</t>
         </is>
       </c>
       <c r="DF15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Detroit Tigers: 10 FS|2026-07-11 @ Detroit Tigers: 13 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 5 FS|2026-07-08 @ Cincinnati Reds: 4 FS|2026-07-07 @ Cincinnati Reds: 0 FS|2026-07-06 @ Kansas City Royals: 8 FS|2026-07-05 @ Kansas City Royals: 15 FS|2026-07-04 @ Kansas City Royals: 5 FS|2026-07-02 vs Pittsburgh Pirates: 3 FS|2026-07-01 vs Pittsburgh Pirates: 8 FS|2026-06-30 vs Pittsburgh Pirates: 10 FS|2026-06-29 vs Pittsburgh Pirates: 5 FS|2026-06-28 @ New York Mets: 3 FS|2026-06-27 @ New York Mets: 2 FS</t>
+          <t>2026-07-12 @ Detroit Tigers: 5 FS|2026-07-11 @ Detroit Tigers: 0 FS|2026-07-10 @ Detroit Tigers: 2 FS|2026-07-09 @ Cincinnati Reds: 2 FS|2026-07-08 @ Cincinnati Reds: 5 FS|2026-07-07 @ Cincinnati Reds: 2 FS|2026-07-06 @ Kansas City Royals: 7 FS|2026-07-05 @ Kansas City Royals: 2 FS|2026-07-04 @ Kansas City Royals: 23 FS|2026-07-02 vs Pittsburgh Pirates: 5 FS|2026-07-01 vs Pittsburgh Pirates: 20 FS|2026-06-30 vs Pittsburgh Pirates: 5 FS|2026-06-29 vs Pittsburgh Pirates: 0 FS|2026-06-28 @ New York Mets: 14 FS|2026-06-26 @ New York Mets: 0 FS</t>
         </is>
       </c>
       <c r="DG15" s="3" t="n">
@@ -11877,10 +11877,10 @@
         <v>30</v>
       </c>
       <c r="DI15" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>6.07</v>
       </c>
       <c r="DJ15" s="3" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="DK15" s="4" t="inlineStr">
         <is>
@@ -11888,54 +11888,54 @@
         </is>
       </c>
       <c r="DL15" s="3" t="n">
-        <v>6</v>
+        <v>3.29</v>
       </c>
       <c r="DM15" s="3" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="DN15" s="3" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="DO15" s="4" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="DP15" s="3" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="DQ15" s="3" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="DR15" s="3" t="n">
+        <v>0.1639</v>
+      </c>
+      <c r="DS15" s="3" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="DT15" s="3" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="DU15" s="3" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="DV15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" s="3" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="DX15" s="3" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="DY15" s="3" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="DZ15" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="DN15" s="3" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="DO15" s="4" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="DP15" s="3" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="DQ15" s="3" t="n">
-        <v>1.542</v>
-      </c>
-      <c r="DR15" s="3" t="n">
-        <v>0.2881</v>
-      </c>
-      <c r="DS15" s="3" t="n">
-        <v>0.0508</v>
-      </c>
-      <c r="DT15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU15" s="3" t="n">
-        <v>0.0678</v>
-      </c>
-      <c r="DV15" s="3" t="n">
-        <v>0.0169</v>
-      </c>
-      <c r="DW15" s="3" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="DX15" s="3" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="DY15" s="3" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="DZ15" s="3" t="n">
-        <v>6.75</v>
-      </c>
       <c r="EA15" s="3" t="n">
-        <v>6.13</v>
+        <v>6.31</v>
       </c>
       <c r="EB15" s="3" t="n">
         <v>28</v>
@@ -11953,25 +11953,25 @@
         <v>20</v>
       </c>
       <c r="EG15" s="3" t="n">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="EH15" s="3" t="n">
-        <v>83.70999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="EI15" s="3" t="n">
-        <v>23.84</v>
+        <v>25.08</v>
       </c>
       <c r="EJ15" s="3" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="EK15" s="3" t="n">
-        <v>29.18</v>
+        <v>32.78</v>
       </c>
       <c r="EL15" s="3" t="n">
-        <v>0.365</v>
+        <v>0.346</v>
       </c>
       <c r="EM15" s="3" t="n">
-        <v>0.9053</v>
+        <v>0.9054</v>
       </c>
       <c r="EN15" s="3" t="n">
         <v>1</v>
@@ -11983,10 +11983,10 @@
         <v>1</v>
       </c>
       <c r="EQ15" s="3" t="n">
-        <v>1.01</v>
+        <v>0.9836</v>
       </c>
       <c r="ER15" s="3" t="n">
-        <v>532</v>
+        <v>443</v>
       </c>
       <c r="ES15" s="4" t="inlineStr">
         <is>
@@ -11994,43 +11994,43 @@
         </is>
       </c>
       <c r="ET15" s="3" t="n">
-        <v>0.1239</v>
+        <v>0.1023</v>
       </c>
       <c r="EU15" s="3" t="n">
-        <v>0.0401</v>
+        <v>0.0354</v>
       </c>
       <c r="EV15" s="3" t="n">
-        <v>0.0058</v>
+        <v>0.0023</v>
       </c>
       <c r="EW15" s="3" t="n">
-        <v>0.0213</v>
+        <v>0.026</v>
       </c>
       <c r="EX15" s="3" t="n">
-        <v>0.0992</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="EY15" s="3" t="n">
-        <v>0.0107</v>
+        <v>0.021</v>
       </c>
       <c r="EZ15" s="3" t="n">
-        <v>0.2074</v>
+        <v>0.1931</v>
       </c>
       <c r="FA15" s="3" t="n">
-        <v>0.4317</v>
+        <v>0.4901</v>
       </c>
       <c r="FB15" s="3" t="n">
-        <v>0.331</v>
+        <v>0.2517</v>
       </c>
       <c r="FC15" s="3" t="n">
-        <v>0.2374</v>
+        <v>0.2582</v>
       </c>
       <c r="FD15" s="3" t="n">
-        <v>0.0953</v>
+        <v>0.0925</v>
       </c>
       <c r="FE15" s="3" t="n">
-        <v>0.1053</v>
+        <v>0.1197</v>
       </c>
       <c r="FF15" s="3" t="n">
-        <v>0.0199</v>
+        <v>0.0083</v>
       </c>
       <c r="FG15" s="3" t="n">
         <v>1</v>
@@ -12041,19 +12041,19 @@
         </is>
       </c>
       <c r="FI15" s="3" t="n">
-        <v>5.43</v>
+        <v>6.48</v>
       </c>
       <c r="FJ15" s="3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="FK15" s="3" t="n">
-        <v>7.82</v>
+        <v>6.96</v>
       </c>
       <c r="FL15" s="3" t="n">
-        <v>13.36</v>
+        <v>14.58</v>
       </c>
       <c r="FM15" s="3" t="n">
-        <v>3.99</v>
+        <v>4.08</v>
       </c>
       <c r="FN15" s="3" t="n">
         <v>0</v>
@@ -12064,85 +12064,85 @@
         </is>
       </c>
       <c r="FP15" s="3" t="n">
-        <v>64.8</v>
+        <v>60</v>
       </c>
       <c r="FQ15" s="3" t="n">
-        <v>64.8</v>
+        <v>50.2</v>
       </c>
       <c r="FR15" s="3" t="n">
-        <v>53.7</v>
+        <v>50.2</v>
       </c>
       <c r="FS15" s="3" t="n">
-        <v>53.7</v>
+        <v>44.4</v>
       </c>
       <c r="FT15" s="3" t="n">
-        <v>48.4</v>
+        <v>44.4</v>
       </c>
       <c r="FU15" s="3" t="n">
-        <v>48.4</v>
+        <v>34.1</v>
       </c>
       <c r="FV15" s="3" t="n">
-        <v>37.4</v>
+        <v>34.1</v>
       </c>
       <c r="FW15" s="3" t="n">
-        <v>34.3</v>
+        <v>31.6</v>
       </c>
       <c r="FX15" s="3" t="n">
-        <v>34.3</v>
+        <v>31.6</v>
       </c>
       <c r="FY15" s="3" t="n">
-        <v>26.8</v>
+        <v>24.8</v>
       </c>
       <c r="FZ15" s="3" t="n">
-        <v>26.8</v>
+        <v>24.8</v>
       </c>
       <c r="GA15" s="3" t="n">
-        <v>23.1</v>
+        <v>24.8</v>
       </c>
       <c r="GB15" s="3" t="n">
-        <v>23.1</v>
+        <v>22.2</v>
       </c>
       <c r="GC15" s="3" t="n">
-        <v>19.6</v>
+        <v>22.2</v>
       </c>
       <c r="GD15" s="3" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="GE15" s="3" t="n">
-        <v>16.3</v>
+        <v>18.8</v>
       </c>
       <c r="GF15" s="3" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="GG15" s="3" t="n">
-        <v>14.3</v>
+        <v>16.5</v>
       </c>
       <c r="GH15" s="3" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="GI15" s="3" t="n">
-        <v>12.3</v>
+        <v>15</v>
       </c>
       <c r="GJ15" s="3" t="n">
-        <v>11.3</v>
+        <v>13.4</v>
       </c>
       <c r="GK15" s="3" t="n">
-        <v>11.3</v>
+        <v>13.4</v>
       </c>
       <c r="GL15" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="GM15" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="GN15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="GO15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="GP15" s="3" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="GQ15" s="3" t="n">
         <v>8</v>
@@ -12271,16 +12271,16 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>6.49</v>
+        <v>6.42</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.63</v>
+        <v>5.53</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>5.63</v>
+        <v>5.53</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>6.74</v>
@@ -12289,13 +12289,13 @@
         <v>6.47</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>6.32</v>
+        <v>6.21</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.024</v>
+        <v>1.042</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>9.4</v>
@@ -12322,88 +12322,88 @@
         </is>
       </c>
       <c r="X16" s="5" t="n">
-        <v>67.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="Z16" s="5" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="AA16" s="6" t="n">
-        <v>52.1</v>
+        <v>58.1</v>
+      </c>
+      <c r="Z16" s="6" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="AA16" s="7" t="n">
+        <v>51.6</v>
       </c>
       <c r="AB16" s="7" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="AC16" s="7" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="AD16" s="7" t="n">
-        <v>40.1</v>
+        <v>50.6</v>
+      </c>
+      <c r="AC16" s="8" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="AD16" s="8" t="n">
+        <v>39.2</v>
       </c>
       <c r="AE16" s="8" t="n">
-        <v>36.9</v>
+        <v>35.8</v>
       </c>
       <c r="AF16" s="8" t="n">
-        <v>36.4</v>
+        <v>35.3</v>
       </c>
       <c r="AG16" s="8" t="n">
-        <v>28.9</v>
+        <v>27.8</v>
       </c>
       <c r="AH16" s="8" t="n">
-        <v>28.4</v>
+        <v>27.3</v>
       </c>
       <c r="AI16" s="8" t="n">
-        <v>26.9</v>
+        <v>25.8</v>
       </c>
       <c r="AJ16" s="8" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="AK16" s="8" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="AL16" s="8" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="AM16" s="8" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="AN16" s="8" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="AO16" s="8" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="AP16" s="8" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="AQ16" s="8" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="AR16" s="8" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="AS16" s="8" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="AT16" s="8" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="AU16" s="8" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="AV16" s="8" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="AW16" s="8" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="AX16" s="8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY16" s="3" t="n">
-        <v>155.01</v>
+        <v>153.16</v>
       </c>
       <c r="AZ16" s="4" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="BA16" s="9" t="inlineStr">
         <is>
-          <t>MORE 3.5 | 58.2% | Edge +2.1</t>
+          <t>MORE 3.0 | 58.1% | Edge +2.5</t>
         </is>
       </c>
       <c r="BB16" s="4" t="inlineStr">
@@ -12421,16 +12421,16 @@
         </is>
       </c>
       <c r="BC16" s="3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BD16" s="3" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="BE16" s="3" t="n">
-        <v>2.13</v>
+        <v>2.53</v>
       </c>
       <c r="BF16" s="3" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="BG16" s="4" t="inlineStr">
         <is>
@@ -12525,23 +12525,23 @@
         <v>1.04</v>
       </c>
       <c r="CG16" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH16" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI16" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ16" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK16" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL16" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM16" s="3" t="n">
@@ -12663,19 +12663,19 @@
         <v>0</v>
       </c>
       <c r="DW16" s="3" t="n">
-        <v>6.21</v>
+        <v>6.14</v>
       </c>
       <c r="DX16" s="3" t="n">
-        <v>6.97</v>
+        <v>6.89</v>
       </c>
       <c r="DY16" s="3" t="n">
-        <v>6.62</v>
+        <v>6.54</v>
       </c>
       <c r="DZ16" s="3" t="n">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="EA16" s="3" t="n">
-        <v>5.9</v>
+        <v>5.83</v>
       </c>
       <c r="EB16" s="3" t="n">
         <v>28</v>
@@ -12737,13 +12737,13 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="EU16" s="3" t="n">
-        <v>0.0434</v>
+        <v>0.042</v>
       </c>
       <c r="EV16" s="3" t="n">
         <v>0.0025</v>
       </c>
       <c r="EW16" s="3" t="n">
-        <v>0.0311</v>
+        <v>0.0301</v>
       </c>
       <c r="EX16" s="3" t="n">
         <v>0.0973</v>
@@ -12781,19 +12781,19 @@
         </is>
       </c>
       <c r="FI16" s="3" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="FJ16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="FK16" s="3" t="n">
-        <v>8.01</v>
+        <v>6.98</v>
       </c>
       <c r="FL16" s="3" t="n">
-        <v>16.2</v>
+        <v>15.31</v>
       </c>
       <c r="FM16" s="3" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="FN16" s="3" t="n">
         <v>0</v>
@@ -12804,85 +12804,85 @@
         </is>
       </c>
       <c r="FP16" s="3" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="FQ16" s="3" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
       <c r="FR16" s="3" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
       <c r="FS16" s="3" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="FT16" s="3" t="n">
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="FU16" s="3" t="n">
-        <v>35.6</v>
+        <v>34.7</v>
       </c>
       <c r="FV16" s="3" t="n">
-        <v>35.6</v>
+        <v>34.7</v>
       </c>
       <c r="FW16" s="3" t="n">
-        <v>32.9</v>
+        <v>31.8</v>
       </c>
       <c r="FX16" s="3" t="n">
-        <v>32.9</v>
+        <v>31.8</v>
       </c>
       <c r="FY16" s="3" t="n">
-        <v>25.9</v>
+        <v>24.8</v>
       </c>
       <c r="FZ16" s="3" t="n">
-        <v>25.9</v>
+        <v>24.8</v>
       </c>
       <c r="GA16" s="3" t="n">
-        <v>25.9</v>
+        <v>24.8</v>
       </c>
       <c r="GB16" s="3" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="GC16" s="3" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="GD16" s="3" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="GE16" s="3" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="GF16" s="3" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="GG16" s="3" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="GH16" s="3" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="GI16" s="3" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="GJ16" s="3" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="GK16" s="3" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="GL16" s="3" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="GM16" s="3" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="GN16" s="3" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="GO16" s="3" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="GP16" s="3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="GQ16" s="3" t="n">
         <v>8</v>
@@ -13011,16 +13011,16 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>6.51</v>
+        <v>6.44</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>6.1</v>
+        <v>5.93</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>6.1</v>
+        <v>5.93</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>5.2</v>
+        <v>4.34</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>4.32</v>
@@ -13029,13 +13029,13 @@
         <v>5.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>3.4</v>
@@ -13062,88 +13062,88 @@
         </is>
       </c>
       <c r="X17" s="5" t="n">
-        <v>82.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>74.8</v>
+        <v>73.7</v>
       </c>
       <c r="Z17" s="5" t="n">
-        <v>74.3</v>
+        <v>73.2</v>
       </c>
       <c r="AA17" s="5" t="n">
-        <v>62.5</v>
+        <v>60.8</v>
       </c>
       <c r="AB17" s="6" t="n">
-        <v>57.8</v>
+        <v>55.9</v>
       </c>
       <c r="AC17" s="7" t="n">
-        <v>56.8</v>
+        <v>54.9</v>
       </c>
       <c r="AD17" s="7" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="AE17" s="7" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="AF17" s="7" t="n">
-        <v>40.7</v>
+        <v>42.8</v>
+      </c>
+      <c r="AE17" s="8" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AF17" s="8" t="n">
+        <v>39</v>
       </c>
       <c r="AG17" s="8" t="n">
-        <v>33.1</v>
+        <v>31.9</v>
       </c>
       <c r="AH17" s="8" t="n">
-        <v>32.6</v>
+        <v>31.4</v>
       </c>
       <c r="AI17" s="8" t="n">
-        <v>26.9</v>
+        <v>25.9</v>
       </c>
       <c r="AJ17" s="8" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="AK17" s="8" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="AL17" s="8" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="AM17" s="8" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="AN17" s="8" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="AO17" s="8" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="AP17" s="8" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="AQ17" s="8" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AR17" s="8" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="AS17" s="8" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="AT17" s="8" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU17" s="8" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV17" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AW17" s="8" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="AX17" s="8" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="AY17" s="3" t="n">
-        <v>153.25</v>
+        <v>150.35</v>
       </c>
       <c r="AZ17" s="4" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="BA17" s="9" t="inlineStr">
         <is>
-          <t>MORE 4.0 | 62.5% | Edge +2.1</t>
+          <t>MORE 4.0 | 60.8% | Edge +1.9</t>
         </is>
       </c>
       <c r="BB17" s="4" t="inlineStr">
@@ -13164,17 +13164,17 @@
         <v>4</v>
       </c>
       <c r="BD17" s="3" t="n">
-        <v>62.5</v>
+        <v>60.8</v>
       </c>
       <c r="BE17" s="3" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="BF17" s="3" t="n">
-        <v>25</v>
+        <v>21.6</v>
       </c>
       <c r="BG17" s="4" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Playable</t>
         </is>
       </c>
       <c r="BH17" s="3" t="n">
@@ -13265,23 +13265,23 @@
         <v>1.04</v>
       </c>
       <c r="CG17" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH17" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI17" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ17" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK17" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL17" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM17" s="3" t="n">
@@ -13403,19 +13403,19 @@
         <v>0</v>
       </c>
       <c r="DW17" s="3" t="n">
-        <v>6.65</v>
+        <v>6.57</v>
       </c>
       <c r="DX17" s="3" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="DY17" s="3" t="n">
         <v>6.12</v>
       </c>
-      <c r="DY17" s="3" t="n">
-        <v>6.19</v>
-      </c>
       <c r="DZ17" s="3" t="n">
-        <v>6.66</v>
+        <v>6.59</v>
       </c>
       <c r="EA17" s="3" t="n">
-        <v>6.81</v>
+        <v>6.73</v>
       </c>
       <c r="EB17" s="3" t="n">
         <v>28</v>
@@ -13477,13 +13477,13 @@
         <v>0.1385</v>
       </c>
       <c r="EU17" s="3" t="n">
-        <v>0.0468</v>
+        <v>0.0453</v>
       </c>
       <c r="EV17" s="3" t="n">
         <v>0.0037</v>
       </c>
       <c r="EW17" s="3" t="n">
-        <v>0.0286</v>
+        <v>0.0276</v>
       </c>
       <c r="EX17" s="3" t="n">
         <v>0.06759999999999999</v>
@@ -13524,16 +13524,16 @@
         <v>5.2</v>
       </c>
       <c r="FJ17" s="3" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="FK17" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>7.64</v>
       </c>
       <c r="FL17" s="3" t="n">
-        <v>14.17</v>
+        <v>13.42</v>
       </c>
       <c r="FM17" s="3" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="FN17" s="3" t="n">
         <v>0</v>
@@ -13544,85 +13544,85 @@
         </is>
       </c>
       <c r="FP17" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="FQ17" s="3" t="n">
-        <v>66.8</v>
+        <v>65.7</v>
       </c>
       <c r="FR17" s="3" t="n">
-        <v>66.8</v>
+        <v>65.7</v>
       </c>
       <c r="FS17" s="3" t="n">
-        <v>55.5</v>
+        <v>53.8</v>
       </c>
       <c r="FT17" s="3" t="n">
-        <v>51.8</v>
+        <v>49.9</v>
       </c>
       <c r="FU17" s="3" t="n">
-        <v>51.8</v>
+        <v>49.9</v>
       </c>
       <c r="FV17" s="3" t="n">
-        <v>39.8</v>
+        <v>38.3</v>
       </c>
       <c r="FW17" s="3" t="n">
-        <v>39.8</v>
+        <v>35.5</v>
       </c>
       <c r="FX17" s="3" t="n">
-        <v>37.2</v>
+        <v>35.5</v>
       </c>
       <c r="FY17" s="3" t="n">
-        <v>30.1</v>
+        <v>28.9</v>
       </c>
       <c r="FZ17" s="3" t="n">
-        <v>30.1</v>
+        <v>28.9</v>
       </c>
       <c r="GA17" s="3" t="n">
-        <v>25.9</v>
+        <v>24.9</v>
       </c>
       <c r="GB17" s="3" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="GC17" s="3" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="GD17" s="3" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="GE17" s="3" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="GF17" s="3" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="GG17" s="3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="GH17" s="3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="GI17" s="3" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="GJ17" s="3" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="GK17" s="3" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="GL17" s="3" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="GM17" s="3" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="GN17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="GO17" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="GP17" s="3" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="GQ17" s="3" t="n">
         <v>8</v>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="HR17" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -13751,16 +13751,16 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>5.32</v>
+        <v>5.29</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>5.95</v>
@@ -13769,13 +13769,13 @@
         <v>5.97</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>5.15</v>
+        <v>5.06</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>5.7</v>
+        <v>5.66</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>1.158</v>
+        <v>1.18</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>8.6</v>
@@ -13802,34 +13802,34 @@
         </is>
       </c>
       <c r="X18" s="6" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="Y18" s="7" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="Z18" s="7" t="n">
-        <v>53.7</v>
+        <v>53.5</v>
       </c>
       <c r="AA18" s="7" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="AB18" s="7" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="AC18" s="8" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="AD18" s="8" t="n">
-        <v>34.3</v>
+        <v>34.5</v>
       </c>
       <c r="AE18" s="8" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="AF18" s="8" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="AG18" s="8" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="AH18" s="8" t="n">
         <v>23</v>
@@ -13838,10 +13838,10 @@
         <v>21.5</v>
       </c>
       <c r="AJ18" s="8" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="AK18" s="8" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="AL18" s="8" t="n">
         <v>14.1</v>
@@ -13853,37 +13853,37 @@
         <v>14.1</v>
       </c>
       <c r="AO18" s="8" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="AP18" s="8" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="AQ18" s="8" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR18" s="8" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS18" s="8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" s="8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU18" s="8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" s="8" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="AW18" s="8" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="AX18" s="8" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AY18" s="3" t="n">
-        <v>133.75</v>
+        <v>132.71</v>
       </c>
       <c r="AZ18" s="4" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
       </c>
       <c r="BA18" s="10" t="inlineStr">
         <is>
-          <t>LESS 5.0 | 65.2% | Edge +0.4</t>
+          <t>LESS 5.0 | 65.0% | Edge +0.4</t>
         </is>
       </c>
       <c r="BB18" s="4" t="inlineStr">
@@ -13904,13 +13904,13 @@
         <v>5</v>
       </c>
       <c r="BD18" s="3" t="n">
-        <v>65.2</v>
+        <v>65</v>
       </c>
       <c r="BE18" s="3" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="BF18" s="3" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="BG18" s="4" t="inlineStr">
         <is>
@@ -14005,23 +14005,23 @@
         <v>1.04</v>
       </c>
       <c r="CG18" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH18" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI18" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ18" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK18" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL18" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM18" s="3" t="n">
@@ -14143,19 +14143,19 @@
         <v>0.0625</v>
       </c>
       <c r="DW18" s="3" t="n">
-        <v>5.25</v>
+        <v>5.21</v>
       </c>
       <c r="DX18" s="3" t="n">
-        <v>5.54</v>
+        <v>5.51</v>
       </c>
       <c r="DY18" s="3" t="n">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="DZ18" s="3" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="EA18" s="3" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="EB18" s="3" t="n">
         <v>28</v>
@@ -14217,13 +14217,13 @@
         <v>0.1401</v>
       </c>
       <c r="EU18" s="3" t="n">
-        <v>0.0316</v>
+        <v>0.0305</v>
       </c>
       <c r="EV18" s="3" t="n">
         <v>0.0056</v>
       </c>
       <c r="EW18" s="3" t="n">
-        <v>0.0155</v>
+        <v>0.015</v>
       </c>
       <c r="EX18" s="3" t="n">
         <v>0.0848</v>
@@ -14261,19 +14261,19 @@
         </is>
       </c>
       <c r="FI18" s="3" t="n">
-        <v>5.7</v>
+        <v>5.66</v>
       </c>
       <c r="FJ18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="FK18" s="3" t="n">
-        <v>7.06</v>
+        <v>7.08</v>
       </c>
       <c r="FL18" s="3" t="n">
-        <v>12.86</v>
+        <v>11.8</v>
       </c>
       <c r="FM18" s="3" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="FN18" s="3" t="n">
         <v>0</v>
@@ -14284,34 +14284,34 @@
         </is>
       </c>
       <c r="FP18" s="3" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="FQ18" s="3" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="FR18" s="3" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="FS18" s="3" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="FT18" s="3" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="FU18" s="3" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="FV18" s="3" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="FW18" s="3" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="FX18" s="3" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="FY18" s="3" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="FZ18" s="3" t="n">
         <v>20.5</v>
@@ -14320,10 +14320,10 @@
         <v>20.5</v>
       </c>
       <c r="GB18" s="3" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="GC18" s="3" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="GD18" s="3" t="n">
         <v>14.1</v>
@@ -14335,34 +14335,34 @@
         <v>14.1</v>
       </c>
       <c r="GG18" s="3" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="GH18" s="3" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="GI18" s="3" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="GJ18" s="3" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="GK18" s="3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="GL18" s="3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="GM18" s="3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="GN18" s="3" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="GO18" s="3" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="GP18" s="3" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="GQ18" s="3" t="n">
         <v>8</v>
@@ -14491,7 +14491,7 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>4.72</v>
@@ -14500,7 +14500,7 @@
         <v>4.72</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>5.33</v>
@@ -14509,13 +14509,13 @@
         <v>5.65</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>5.72</v>
+        <v>5.62</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>0.988</v>
+        <v>1.006</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>2.4</v>
@@ -14542,88 +14542,88 @@
         </is>
       </c>
       <c r="X19" s="5" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="Y19" s="5" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="Z19" s="6" t="n">
-        <v>51.2</v>
+        <v>63</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="Z19" s="7" t="n">
+        <v>52</v>
       </c>
       <c r="AA19" s="7" t="n">
-        <v>50.7</v>
+        <v>46.4</v>
       </c>
       <c r="AB19" s="7" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
       <c r="AC19" s="8" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="AD19" s="8" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="AF19" s="8" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="AG19" s="8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AH19" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="AH19" s="8" t="n">
-        <v>23</v>
-      </c>
       <c r="AI19" s="8" t="n">
-        <v>19.3</v>
+        <v>22</v>
       </c>
       <c r="AJ19" s="8" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AK19" s="8" t="n">
-        <v>15.4</v>
+        <v>18.4</v>
       </c>
       <c r="AL19" s="8" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="AM19" s="8" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AN19" s="8" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="AO19" s="8" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="AP19" s="8" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="AQ19" s="8" t="n">
-        <v>10.7</v>
+        <v>12.2</v>
       </c>
       <c r="AR19" s="8" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="AS19" s="8" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="AT19" s="8" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="AU19" s="8" t="n">
-        <v>7.7</v>
+        <v>10.3</v>
       </c>
       <c r="AV19" s="8" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AW19" s="8" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AX19" s="8" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="AY19" s="3" t="n">
-        <v>123.33</v>
+        <v>123.32</v>
       </c>
       <c r="AZ19" s="4" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="BA19" s="9" t="inlineStr">
         <is>
-          <t>MORE 3.0 | 62.7% | Edge +1.7</t>
+          <t>MORE 2.5 | 63.0% | Edge +2.2</t>
         </is>
       </c>
       <c r="BB19" s="4" t="inlineStr">
@@ -14641,16 +14641,16 @@
         </is>
       </c>
       <c r="BC19" s="3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BD19" s="3" t="n">
-        <v>62.7</v>
+        <v>63</v>
       </c>
       <c r="BE19" s="3" t="n">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="BF19" s="3" t="n">
-        <v>25.4</v>
+        <v>26</v>
       </c>
       <c r="BG19" s="4" t="inlineStr">
         <is>
@@ -14745,23 +14745,23 @@
         <v>1.04</v>
       </c>
       <c r="CG19" s="3" t="n">
-        <v>1.065</v>
+        <v>1.03</v>
       </c>
       <c r="CH19" s="3" t="n">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="CI19" s="3" t="n">
-        <v>12.8</v>
+        <v>9.9</v>
       </c>
       <c r="CJ19" s="3" t="n">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="CK19" s="3" t="n">
         <v>9</v>
       </c>
       <c r="CL19" s="4" t="inlineStr">
         <is>
-          <t>hot, light wind</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CM19" s="3" t="n">
@@ -14883,19 +14883,19 @@
         <v>0</v>
       </c>
       <c r="DW19" s="3" t="n">
-        <v>5.04</v>
+        <v>4.99</v>
       </c>
       <c r="DX19" s="3" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="DY19" s="3" t="n">
-        <v>5.02</v>
+        <v>4.97</v>
       </c>
       <c r="DZ19" s="3" t="n">
-        <v>5.29</v>
+        <v>5.23</v>
       </c>
       <c r="EA19" s="3" t="n">
-        <v>4.87</v>
+        <v>4.82</v>
       </c>
       <c r="EB19" s="3" t="n">
         <v>28</v>
@@ -14957,13 +14957,13 @@
         <v>0.101</v>
       </c>
       <c r="EU19" s="3" t="n">
-        <v>0.0368</v>
+        <v>0.0356</v>
       </c>
       <c r="EV19" s="3" t="n">
         <v>0.0028</v>
       </c>
       <c r="EW19" s="3" t="n">
-        <v>0.0237</v>
+        <v>0.0229</v>
       </c>
       <c r="EX19" s="3" t="n">
         <v>0.0853</v>
@@ -15001,19 +15001,19 @@
         </is>
       </c>
       <c r="FI19" s="3" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="FJ19" s="3" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="FK19" s="3" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="FL19" s="3" t="n">
-        <v>13.89</v>
+        <v>14.04</v>
       </c>
       <c r="FM19" s="3" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="FN19" s="3" t="n">
         <v>0</v>
@@ -15024,85 +15024,85 @@
         </is>
       </c>
       <c r="FP19" s="3" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="FQ19" s="3" t="n">
-        <v>54.7</v>
+        <v>44.5</v>
       </c>
       <c r="FR19" s="3" t="n">
-        <v>43.7</v>
+        <v>44.5</v>
       </c>
       <c r="FS19" s="3" t="n">
-        <v>43.7</v>
+        <v>39.4</v>
       </c>
       <c r="FT19" s="3" t="n">
-        <v>39</v>
+        <v>39.4</v>
       </c>
       <c r="FU19" s="3" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="FV19" s="3" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="FW19" s="3" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="FX19" s="3" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="FY19" s="3" t="n">
-        <v>20.5</v>
+        <v>26.9</v>
       </c>
       <c r="FZ19" s="3" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="GA19" s="3" t="n">
-        <v>18.3</v>
+        <v>21</v>
       </c>
       <c r="GB19" s="3" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="GC19" s="3" t="n">
-        <v>15.4</v>
+        <v>18.4</v>
       </c>
       <c r="GD19" s="3" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="GE19" s="3" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="GF19" s="3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="GG19" s="3" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="GH19" s="3" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="GI19" s="3" t="n">
-        <v>10.7</v>
+        <v>12.2</v>
       </c>
       <c r="GJ19" s="3" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="GK19" s="3" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="GL19" s="3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="GM19" s="3" t="n">
-        <v>7.7</v>
+        <v>10.3</v>
       </c>
       <c r="GN19" s="3" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="GO19" s="3" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="GP19" s="3" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="GQ19" s="3" t="n">
         <v>8</v>
